--- a/BWI/bestwine_output/bestwine_Brazil.xlsx
+++ b/BWI/bestwine_output/bestwine_Brazil.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA690"/>
+  <dimension ref="A1:AA695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -74922,6 +74922,555 @@
         </is>
       </c>
     </row>
+    <row r="691">
+      <c r="A691" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda</t>
+        </is>
+      </c>
+      <c r="B691" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda.</t>
+        </is>
+      </c>
+      <c r="C691" s="2" t="inlineStr">
+        <is>
+          <t>121210</t>
+        </is>
+      </c>
+      <c r="D691" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E691" s="2" t="inlineStr">
+        <is>
+          <t>Moema</t>
+        </is>
+      </c>
+      <c r="F691" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G691" s="2" t="inlineStr">
+        <is>
+          <t>60 Avenida Rouxinol</t>
+        </is>
+      </c>
+      <c r="H691" s="2" t="inlineStr">
+        <is>
+          <t>04516-000</t>
+        </is>
+      </c>
+      <c r="I691" s="2" t="inlineStr">
+        <is>
+          <t>https://www.importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="J691" s="2" t="inlineStr"/>
+      <c r="K691" s="2" t="inlineStr"/>
+      <c r="L691" s="2" t="inlineStr"/>
+      <c r="M691" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N691" s="2" t="inlineStr">
+        <is>
+          <t>patricia.martins@importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="O691" s="2" t="inlineStr">
+        <is>
+          <t>+55 47 3048-0609</t>
+        </is>
+      </c>
+      <c r="P691" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q691" s="2" t="inlineStr">
+        <is>
+          <t>24004841000135</t>
+        </is>
+      </c>
+      <c r="R691" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boena-importadora/</t>
+        </is>
+      </c>
+      <c r="S691" s="2" t="inlineStr"/>
+      <c r="T691" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boenaimportadora/</t>
+        </is>
+      </c>
+      <c r="U691" s="2" t="inlineStr"/>
+      <c r="V691" s="2" t="inlineStr"/>
+      <c r="W691" s="2" t="inlineStr">
+        <is>
+          <t>Newton Carlos</t>
+        </is>
+      </c>
+      <c r="X691" s="2" t="inlineStr">
+        <is>
+          <t>National Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y691" s="2" t="inlineStr"/>
+      <c r="Z691" s="2" t="inlineStr"/>
+      <c r="AA691" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/newton-carlos-almeida-9b40a458/</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda</t>
+        </is>
+      </c>
+      <c r="B692" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda.</t>
+        </is>
+      </c>
+      <c r="C692" s="2" t="inlineStr">
+        <is>
+          <t>121210</t>
+        </is>
+      </c>
+      <c r="D692" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E692" s="2" t="inlineStr">
+        <is>
+          <t>Moema</t>
+        </is>
+      </c>
+      <c r="F692" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G692" s="2" t="inlineStr">
+        <is>
+          <t>60 Avenida Rouxinol</t>
+        </is>
+      </c>
+      <c r="H692" s="2" t="inlineStr">
+        <is>
+          <t>04516-000</t>
+        </is>
+      </c>
+      <c r="I692" s="2" t="inlineStr">
+        <is>
+          <t>https://www.importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="J692" s="2" t="inlineStr"/>
+      <c r="K692" s="2" t="inlineStr"/>
+      <c r="L692" s="2" t="inlineStr"/>
+      <c r="M692" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N692" s="2" t="inlineStr">
+        <is>
+          <t>patricia.martins@importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="O692" s="2" t="inlineStr">
+        <is>
+          <t>+55 47 3048-0609</t>
+        </is>
+      </c>
+      <c r="P692" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q692" s="2" t="inlineStr">
+        <is>
+          <t>24004841000135</t>
+        </is>
+      </c>
+      <c r="R692" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boena-importadora/</t>
+        </is>
+      </c>
+      <c r="S692" s="2" t="inlineStr"/>
+      <c r="T692" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boenaimportadora/</t>
+        </is>
+      </c>
+      <c r="U692" s="2" t="inlineStr"/>
+      <c r="V692" s="2" t="inlineStr"/>
+      <c r="W692" s="2" t="inlineStr">
+        <is>
+          <t>Patricia F</t>
+        </is>
+      </c>
+      <c r="X692" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Manager</t>
+        </is>
+      </c>
+      <c r="Y692" s="2" t="inlineStr"/>
+      <c r="Z692" s="2" t="inlineStr"/>
+      <c r="AA692" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricia-f-martins-643a4320b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="B693" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="C693" s="2" t="inlineStr">
+        <is>
+          <t>25723</t>
+        </is>
+      </c>
+      <c r="D693" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E693" s="2" t="inlineStr">
+        <is>
+          <t>Imperial de São Cristóvão</t>
+        </is>
+      </c>
+      <c r="F693" s="2" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G693" s="2" t="inlineStr">
+        <is>
+          <t>316 Avenida Pedro II</t>
+        </is>
+      </c>
+      <c r="H693" s="2" t="inlineStr">
+        <is>
+          <t>20941-070</t>
+        </is>
+      </c>
+      <c r="I693" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lojaenoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="J693" s="2" t="inlineStr"/>
+      <c r="K693" s="2" t="inlineStr"/>
+      <c r="L693" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M693" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N693" s="2" t="inlineStr">
+        <is>
+          <t>tsalame@enoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="O693" s="2" t="inlineStr">
+        <is>
+          <t>+55 21 2042-8980</t>
+        </is>
+      </c>
+      <c r="P693" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q693" s="2" t="inlineStr">
+        <is>
+          <t>20345380000103</t>
+        </is>
+      </c>
+      <c r="R693" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enoeventos-importadora-de-bebidas-ltda-/</t>
+        </is>
+      </c>
+      <c r="S693" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="T693" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="U693" s="2" t="inlineStr"/>
+      <c r="V693" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@EnoeventosImportadora</t>
+        </is>
+      </c>
+      <c r="W693" s="2" t="inlineStr">
+        <is>
+          <t>Thiago Salame</t>
+        </is>
+      </c>
+      <c r="X693" s="2" t="inlineStr">
+        <is>
+          <t>Partner - Director</t>
+        </is>
+      </c>
+      <c r="Y693" s="2" t="inlineStr"/>
+      <c r="Z693" s="2" t="inlineStr"/>
+      <c r="AA693" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thiago-salame-b2511024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="B694" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="C694" s="2" t="inlineStr">
+        <is>
+          <t>25723</t>
+        </is>
+      </c>
+      <c r="D694" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E694" s="2" t="inlineStr">
+        <is>
+          <t>Imperial de São Cristóvão</t>
+        </is>
+      </c>
+      <c r="F694" s="2" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G694" s="2" t="inlineStr">
+        <is>
+          <t>316 Avenida Pedro II</t>
+        </is>
+      </c>
+      <c r="H694" s="2" t="inlineStr">
+        <is>
+          <t>20941-070</t>
+        </is>
+      </c>
+      <c r="I694" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lojaenoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="J694" s="2" t="inlineStr"/>
+      <c r="K694" s="2" t="inlineStr"/>
+      <c r="L694" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M694" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N694" s="2" t="inlineStr">
+        <is>
+          <t>tsalame@enoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="O694" s="2" t="inlineStr">
+        <is>
+          <t>+55 21 2042-8980</t>
+        </is>
+      </c>
+      <c r="P694" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q694" s="2" t="inlineStr">
+        <is>
+          <t>20345380000103</t>
+        </is>
+      </c>
+      <c r="R694" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enoeventos-importadora-de-bebidas-ltda-/</t>
+        </is>
+      </c>
+      <c r="S694" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="T694" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="U694" s="2" t="inlineStr"/>
+      <c r="V694" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@EnoeventosImportadora</t>
+        </is>
+      </c>
+      <c r="W694" s="2" t="inlineStr">
+        <is>
+          <t>Oscar Daudt</t>
+        </is>
+      </c>
+      <c r="X694" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y694" s="2" t="inlineStr"/>
+      <c r="Z694" s="2" t="inlineStr"/>
+      <c r="AA694" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/oscar-daudt-554623a2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="inlineStr">
+        <is>
+          <t>Hannover Comercio Importacao E Exportacao Ltda</t>
+        </is>
+      </c>
+      <c r="B695" s="2" t="inlineStr">
+        <is>
+          <t>Hannover Comercio Importacao E Exportacao Ltda</t>
+        </is>
+      </c>
+      <c r="C695" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="D695" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E695" s="2" t="inlineStr">
+        <is>
+          <t>Santa Maria Goretti</t>
+        </is>
+      </c>
+      <c r="F695" s="2" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G695" s="2" t="inlineStr">
+        <is>
+          <t>710 Rua Cerro Azul</t>
+        </is>
+      </c>
+      <c r="H695" s="2" t="inlineStr">
+        <is>
+          <t>91030-250</t>
+        </is>
+      </c>
+      <c r="I695" s="2" t="inlineStr">
+        <is>
+          <t>http://www.hannovervinhos.com.br</t>
+        </is>
+      </c>
+      <c r="J695" s="2" t="inlineStr"/>
+      <c r="K695" s="2" t="inlineStr"/>
+      <c r="L695" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M695" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N695" s="2" t="inlineStr">
+        <is>
+          <t>hannover@hannovervinhos.com.br</t>
+        </is>
+      </c>
+      <c r="O695" s="2" t="inlineStr">
+        <is>
+          <t>+55 51 3337-3890</t>
+        </is>
+      </c>
+      <c r="P695" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q695" s="2" t="inlineStr">
+        <is>
+          <t>91636944000105</t>
+        </is>
+      </c>
+      <c r="R695" s="2" t="inlineStr"/>
+      <c r="S695" s="2" t="inlineStr"/>
+      <c r="T695" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hannovervinhos/</t>
+        </is>
+      </c>
+      <c r="U695" s="2" t="inlineStr"/>
+      <c r="V695" s="2" t="inlineStr"/>
+      <c r="W695" s="2" t="inlineStr">
+        <is>
+          <t>Sergio Fernandes</t>
+        </is>
+      </c>
+      <c r="X695" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y695" s="2" t="inlineStr"/>
+      <c r="Z695" s="2" t="inlineStr"/>
+      <c r="AA695" s="2" t="inlineStr">
+        <is>
+          <t>https://br.linkedin.com/in/sergio-fernandes-36aa3b54/en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Brazil.xlsx
+++ b/BWI/bestwine_output/bestwine_Brazil.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA695"/>
+  <dimension ref="A1:AA704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -75471,6 +75471,975 @@
         </is>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" s="2" t="inlineStr">
+        <is>
+          <t>L.s.a. Correa - Vinhos</t>
+        </is>
+      </c>
+      <c r="B696" s="2" t="inlineStr">
+        <is>
+          <t>L.s.a. Correa - Vinhos</t>
+        </is>
+      </c>
+      <c r="C696" s="2" t="inlineStr">
+        <is>
+          <t>111910</t>
+        </is>
+      </c>
+      <c r="D696" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E696" s="2" t="inlineStr">
+        <is>
+          <t>Gonzaga</t>
+        </is>
+      </c>
+      <c r="F696" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Santos</t>
+        </is>
+      </c>
+      <c r="G696" s="2" t="inlineStr">
+        <is>
+          <t>59 Avenida Ana Costa</t>
+        </is>
+      </c>
+      <c r="H696" s="2" t="inlineStr">
+        <is>
+          <t>11060-001</t>
+        </is>
+      </c>
+      <c r="I696" s="2" t="inlineStr">
+        <is>
+          <t>https://wine2go.com.br</t>
+        </is>
+      </c>
+      <c r="J696" s="2" t="inlineStr"/>
+      <c r="K696" s="2" t="inlineStr"/>
+      <c r="L696" s="2" t="inlineStr"/>
+      <c r="M696" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N696" s="2" t="inlineStr">
+        <is>
+          <t>fernanda@wine2go.com.br</t>
+        </is>
+      </c>
+      <c r="O696" s="2" t="inlineStr"/>
+      <c r="P696" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q696" s="2" t="inlineStr"/>
+      <c r="R696" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine2go-brasil/</t>
+        </is>
+      </c>
+      <c r="S696" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wine2gobrasil/</t>
+        </is>
+      </c>
+      <c r="T696" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine2gobrasil</t>
+        </is>
+      </c>
+      <c r="U696" s="2" t="inlineStr"/>
+      <c r="V696" s="2" t="inlineStr"/>
+      <c r="W696" s="2" t="inlineStr">
+        <is>
+          <t>Fernanda Barreiros</t>
+        </is>
+      </c>
+      <c r="X696" s="2" t="inlineStr">
+        <is>
+          <t>Business Partner</t>
+        </is>
+      </c>
+      <c r="Y696" s="2" t="inlineStr"/>
+      <c r="Z696" s="2" t="inlineStr"/>
+      <c r="AA696" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernanda-barreiros-2b8402270/</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="inlineStr">
+        <is>
+          <t>Cmp - Comércio, Importação E Exportação De Bebidas E Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="B697" s="2" t="inlineStr">
+        <is>
+          <t>Cmp - Comércio, Importação E Exportação De Bebidas E Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="C697" s="2" t="inlineStr">
+        <is>
+          <t>40916</t>
+        </is>
+      </c>
+      <c r="D697" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E697" s="2" t="inlineStr">
+        <is>
+          <t>Itaim Bibi</t>
+        </is>
+      </c>
+      <c r="F697" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G697" s="2" t="inlineStr">
+        <is>
+          <t>162 Rua Romilda Margarida Gabriel</t>
+        </is>
+      </c>
+      <c r="H697" s="2" t="inlineStr">
+        <is>
+          <t>04530-090</t>
+        </is>
+      </c>
+      <c r="I697" s="2" t="inlineStr">
+        <is>
+          <t>https://caveleman.com</t>
+        </is>
+      </c>
+      <c r="J697" s="2" t="inlineStr"/>
+      <c r="K697" s="2" t="inlineStr"/>
+      <c r="L697" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M697" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N697" s="2" t="inlineStr">
+        <is>
+          <t>marcio.morelli@caveleman.com.br</t>
+        </is>
+      </c>
+      <c r="O697" s="2" t="inlineStr"/>
+      <c r="P697" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q697" s="2" t="inlineStr">
+        <is>
+          <t>29686483000101</t>
+        </is>
+      </c>
+      <c r="R697" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cave-leman/</t>
+        </is>
+      </c>
+      <c r="S697" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.facebook.com/caveleman/</t>
+        </is>
+      </c>
+      <c r="T697" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/caveleman</t>
+        </is>
+      </c>
+      <c r="U697" s="2" t="inlineStr"/>
+      <c r="V697" s="2" t="inlineStr"/>
+      <c r="W697" s="2" t="inlineStr">
+        <is>
+          <t>Marcio Morelli</t>
+        </is>
+      </c>
+      <c r="X697" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y697" s="2" t="inlineStr"/>
+      <c r="Z697" s="2" t="inlineStr"/>
+      <c r="AA697" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marciomorelli/</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="inlineStr">
+        <is>
+          <t>Cmp - Comércio, Importação E Exportação De Bebidas E Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="B698" s="2" t="inlineStr">
+        <is>
+          <t>Cmp - Comércio, Importação E Exportação De Bebidas E Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="C698" s="2" t="inlineStr">
+        <is>
+          <t>40916</t>
+        </is>
+      </c>
+      <c r="D698" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E698" s="2" t="inlineStr">
+        <is>
+          <t>Itaim Bibi</t>
+        </is>
+      </c>
+      <c r="F698" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G698" s="2" t="inlineStr">
+        <is>
+          <t>162 Rua Romilda Margarida Gabriel</t>
+        </is>
+      </c>
+      <c r="H698" s="2" t="inlineStr">
+        <is>
+          <t>04530-090</t>
+        </is>
+      </c>
+      <c r="I698" s="2" t="inlineStr">
+        <is>
+          <t>https://caveleman.com</t>
+        </is>
+      </c>
+      <c r="J698" s="2" t="inlineStr"/>
+      <c r="K698" s="2" t="inlineStr"/>
+      <c r="L698" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M698" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N698" s="2" t="inlineStr">
+        <is>
+          <t>marcio.morelli@caveleman.com.br</t>
+        </is>
+      </c>
+      <c r="O698" s="2" t="inlineStr"/>
+      <c r="P698" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q698" s="2" t="inlineStr">
+        <is>
+          <t>29686483000101</t>
+        </is>
+      </c>
+      <c r="R698" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cave-leman/</t>
+        </is>
+      </c>
+      <c r="S698" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.facebook.com/caveleman/</t>
+        </is>
+      </c>
+      <c r="T698" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/caveleman</t>
+        </is>
+      </c>
+      <c r="U698" s="2" t="inlineStr"/>
+      <c r="V698" s="2" t="inlineStr"/>
+      <c r="W698" s="2" t="inlineStr">
+        <is>
+          <t>Lucas Toledo</t>
+        </is>
+      </c>
+      <c r="X698" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Representative</t>
+        </is>
+      </c>
+      <c r="Y698" s="2" t="inlineStr"/>
+      <c r="Z698" s="2" t="inlineStr"/>
+      <c r="AA698" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lucas-toledo-piza-amighini-8ab139137/</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="inlineStr">
+        <is>
+          <t>Comercial De Queijos E Vinhos Batel Eireli</t>
+        </is>
+      </c>
+      <c r="B699" s="2" t="inlineStr">
+        <is>
+          <t>Comercial De Queijos E Vinhos Batel Eireli</t>
+        </is>
+      </c>
+      <c r="C699" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D699" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E699" s="2" t="inlineStr">
+        <is>
+          <t>Batel</t>
+        </is>
+      </c>
+      <c r="F699" s="2" t="inlineStr">
+        <is>
+          <t>Paraná, Curitiba</t>
+        </is>
+      </c>
+      <c r="G699" s="2" t="inlineStr">
+        <is>
+          <t>1865 Avenida Sete de Setembro</t>
+        </is>
+      </c>
+      <c r="H699" s="2" t="inlineStr">
+        <is>
+          <t>80060-070</t>
+        </is>
+      </c>
+      <c r="I699" s="2" t="inlineStr">
+        <is>
+          <t>https://adegacuritibana.com.br</t>
+        </is>
+      </c>
+      <c r="J699" s="2" t="inlineStr"/>
+      <c r="K699" s="2" t="inlineStr"/>
+      <c r="L699" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M699" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N699" s="2" t="inlineStr">
+        <is>
+          <t>sac@adegacuritibana.com.br</t>
+        </is>
+      </c>
+      <c r="O699" s="2" t="inlineStr"/>
+      <c r="P699" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q699" s="2" t="inlineStr">
+        <is>
+          <t>09025700000105</t>
+        </is>
+      </c>
+      <c r="R699" s="2" t="inlineStr"/>
+      <c r="S699" s="2" t="inlineStr"/>
+      <c r="T699" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/adegacuritibana/</t>
+        </is>
+      </c>
+      <c r="U699" s="2" t="inlineStr"/>
+      <c r="V699" s="2" t="inlineStr"/>
+      <c r="W699" s="2" t="inlineStr">
+        <is>
+          <t>Maricel Heiden</t>
+        </is>
+      </c>
+      <c r="X699" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y699" s="2" t="inlineStr"/>
+      <c r="Z699" s="2" t="inlineStr"/>
+      <c r="AA699" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maricel-heiden-235a6a5b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda</t>
+        </is>
+      </c>
+      <c r="B700" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda.</t>
+        </is>
+      </c>
+      <c r="C700" s="2" t="inlineStr">
+        <is>
+          <t>121210</t>
+        </is>
+      </c>
+      <c r="D700" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E700" s="2" t="inlineStr">
+        <is>
+          <t>Moema</t>
+        </is>
+      </c>
+      <c r="F700" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G700" s="2" t="inlineStr">
+        <is>
+          <t>60 Avenida Rouxinol</t>
+        </is>
+      </c>
+      <c r="H700" s="2" t="inlineStr">
+        <is>
+          <t>04516-000</t>
+        </is>
+      </c>
+      <c r="I700" s="2" t="inlineStr">
+        <is>
+          <t>https://www.importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="J700" s="2" t="inlineStr"/>
+      <c r="K700" s="2" t="inlineStr"/>
+      <c r="L700" s="2" t="inlineStr"/>
+      <c r="M700" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N700" s="2" t="inlineStr">
+        <is>
+          <t>patricia.martins@importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="O700" s="2" t="inlineStr">
+        <is>
+          <t>+55 47 3048-0609</t>
+        </is>
+      </c>
+      <c r="P700" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q700" s="2" t="inlineStr">
+        <is>
+          <t>24004841000135</t>
+        </is>
+      </c>
+      <c r="R700" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boena-importadora/</t>
+        </is>
+      </c>
+      <c r="S700" s="2" t="inlineStr"/>
+      <c r="T700" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boenaimportadora/</t>
+        </is>
+      </c>
+      <c r="U700" s="2" t="inlineStr"/>
+      <c r="V700" s="2" t="inlineStr"/>
+      <c r="W700" s="2" t="inlineStr">
+        <is>
+          <t>Newton Carlos</t>
+        </is>
+      </c>
+      <c r="X700" s="2" t="inlineStr">
+        <is>
+          <t>National Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y700" s="2" t="inlineStr"/>
+      <c r="Z700" s="2" t="inlineStr"/>
+      <c r="AA700" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/newton-carlos-almeida-9b40a458/</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda</t>
+        </is>
+      </c>
+      <c r="B701" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda.</t>
+        </is>
+      </c>
+      <c r="C701" s="2" t="inlineStr">
+        <is>
+          <t>121210</t>
+        </is>
+      </c>
+      <c r="D701" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E701" s="2" t="inlineStr">
+        <is>
+          <t>Moema</t>
+        </is>
+      </c>
+      <c r="F701" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G701" s="2" t="inlineStr">
+        <is>
+          <t>60 Avenida Rouxinol</t>
+        </is>
+      </c>
+      <c r="H701" s="2" t="inlineStr">
+        <is>
+          <t>04516-000</t>
+        </is>
+      </c>
+      <c r="I701" s="2" t="inlineStr">
+        <is>
+          <t>https://www.importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="J701" s="2" t="inlineStr"/>
+      <c r="K701" s="2" t="inlineStr"/>
+      <c r="L701" s="2" t="inlineStr"/>
+      <c r="M701" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N701" s="2" t="inlineStr">
+        <is>
+          <t>patricia.martins@importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="O701" s="2" t="inlineStr">
+        <is>
+          <t>+55 47 3048-0609</t>
+        </is>
+      </c>
+      <c r="P701" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q701" s="2" t="inlineStr">
+        <is>
+          <t>24004841000135</t>
+        </is>
+      </c>
+      <c r="R701" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boena-importadora/</t>
+        </is>
+      </c>
+      <c r="S701" s="2" t="inlineStr"/>
+      <c r="T701" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boenaimportadora/</t>
+        </is>
+      </c>
+      <c r="U701" s="2" t="inlineStr"/>
+      <c r="V701" s="2" t="inlineStr"/>
+      <c r="W701" s="2" t="inlineStr">
+        <is>
+          <t>Patricia F</t>
+        </is>
+      </c>
+      <c r="X701" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Manager</t>
+        </is>
+      </c>
+      <c r="Y701" s="2" t="inlineStr"/>
+      <c r="Z701" s="2" t="inlineStr"/>
+      <c r="AA701" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricia-f-martins-643a4320b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="B702" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="C702" s="2" t="inlineStr">
+        <is>
+          <t>25723</t>
+        </is>
+      </c>
+      <c r="D702" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E702" s="2" t="inlineStr">
+        <is>
+          <t>Imperial de São Cristóvão</t>
+        </is>
+      </c>
+      <c r="F702" s="2" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G702" s="2" t="inlineStr">
+        <is>
+          <t>316 Avenida Pedro II</t>
+        </is>
+      </c>
+      <c r="H702" s="2" t="inlineStr">
+        <is>
+          <t>20941-070</t>
+        </is>
+      </c>
+      <c r="I702" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lojaenoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="J702" s="2" t="inlineStr"/>
+      <c r="K702" s="2" t="inlineStr"/>
+      <c r="L702" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M702" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N702" s="2" t="inlineStr">
+        <is>
+          <t>tsalame@enoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="O702" s="2" t="inlineStr">
+        <is>
+          <t>+55 21 2042-8980</t>
+        </is>
+      </c>
+      <c r="P702" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q702" s="2" t="inlineStr">
+        <is>
+          <t>20345380000103</t>
+        </is>
+      </c>
+      <c r="R702" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enoeventos-importadora-de-bebidas-ltda-/</t>
+        </is>
+      </c>
+      <c r="S702" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="T702" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="U702" s="2" t="inlineStr"/>
+      <c r="V702" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@EnoeventosImportadora</t>
+        </is>
+      </c>
+      <c r="W702" s="2" t="inlineStr">
+        <is>
+          <t>Thiago Salame</t>
+        </is>
+      </c>
+      <c r="X702" s="2" t="inlineStr">
+        <is>
+          <t>Partner - Director</t>
+        </is>
+      </c>
+      <c r="Y702" s="2" t="inlineStr"/>
+      <c r="Z702" s="2" t="inlineStr"/>
+      <c r="AA702" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thiago-salame-b2511024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="B703" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="C703" s="2" t="inlineStr">
+        <is>
+          <t>25723</t>
+        </is>
+      </c>
+      <c r="D703" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E703" s="2" t="inlineStr">
+        <is>
+          <t>Imperial de São Cristóvão</t>
+        </is>
+      </c>
+      <c r="F703" s="2" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G703" s="2" t="inlineStr">
+        <is>
+          <t>316 Avenida Pedro II</t>
+        </is>
+      </c>
+      <c r="H703" s="2" t="inlineStr">
+        <is>
+          <t>20941-070</t>
+        </is>
+      </c>
+      <c r="I703" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lojaenoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="J703" s="2" t="inlineStr"/>
+      <c r="K703" s="2" t="inlineStr"/>
+      <c r="L703" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M703" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N703" s="2" t="inlineStr">
+        <is>
+          <t>tsalame@enoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="O703" s="2" t="inlineStr">
+        <is>
+          <t>+55 21 2042-8980</t>
+        </is>
+      </c>
+      <c r="P703" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q703" s="2" t="inlineStr">
+        <is>
+          <t>20345380000103</t>
+        </is>
+      </c>
+      <c r="R703" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enoeventos-importadora-de-bebidas-ltda-/</t>
+        </is>
+      </c>
+      <c r="S703" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="T703" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="U703" s="2" t="inlineStr"/>
+      <c r="V703" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@EnoeventosImportadora</t>
+        </is>
+      </c>
+      <c r="W703" s="2" t="inlineStr">
+        <is>
+          <t>Oscar Daudt</t>
+        </is>
+      </c>
+      <c r="X703" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y703" s="2" t="inlineStr"/>
+      <c r="Z703" s="2" t="inlineStr"/>
+      <c r="AA703" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/oscar-daudt-554623a2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="inlineStr">
+        <is>
+          <t>Hannover Comercio Importacao E Exportacao Ltda</t>
+        </is>
+      </c>
+      <c r="B704" s="2" t="inlineStr">
+        <is>
+          <t>Hannover Comercio Importacao E Exportacao Ltda</t>
+        </is>
+      </c>
+      <c r="C704" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="D704" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E704" s="2" t="inlineStr">
+        <is>
+          <t>Santa Maria Goretti</t>
+        </is>
+      </c>
+      <c r="F704" s="2" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G704" s="2" t="inlineStr">
+        <is>
+          <t>710 Rua Cerro Azul</t>
+        </is>
+      </c>
+      <c r="H704" s="2" t="inlineStr">
+        <is>
+          <t>91030-250</t>
+        </is>
+      </c>
+      <c r="I704" s="2" t="inlineStr">
+        <is>
+          <t>http://www.hannovervinhos.com.br</t>
+        </is>
+      </c>
+      <c r="J704" s="2" t="inlineStr"/>
+      <c r="K704" s="2" t="inlineStr"/>
+      <c r="L704" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M704" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N704" s="2" t="inlineStr">
+        <is>
+          <t>hannover@hannovervinhos.com.br</t>
+        </is>
+      </c>
+      <c r="O704" s="2" t="inlineStr">
+        <is>
+          <t>+55 51 3337-3890</t>
+        </is>
+      </c>
+      <c r="P704" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q704" s="2" t="inlineStr">
+        <is>
+          <t>91636944000105</t>
+        </is>
+      </c>
+      <c r="R704" s="2" t="inlineStr"/>
+      <c r="S704" s="2" t="inlineStr"/>
+      <c r="T704" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hannovervinhos/</t>
+        </is>
+      </c>
+      <c r="U704" s="2" t="inlineStr"/>
+      <c r="V704" s="2" t="inlineStr"/>
+      <c r="W704" s="2" t="inlineStr">
+        <is>
+          <t>Sergio Fernandes</t>
+        </is>
+      </c>
+      <c r="X704" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y704" s="2" t="inlineStr"/>
+      <c r="Z704" s="2" t="inlineStr"/>
+      <c r="AA704" s="2" t="inlineStr">
+        <is>
+          <t>https://br.linkedin.com/in/sergio-fernandes-36aa3b54/en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Brazil.xlsx
+++ b/BWI/bestwine_output/bestwine_Brazil.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA704"/>
+  <dimension ref="A1:AA736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -76440,6 +76440,3418 @@
         </is>
       </c>
     </row>
+    <row r="705">
+      <c r="A705" s="2" t="inlineStr">
+        <is>
+          <t>Vero Do Brasil Industria E Comercio Eireli</t>
+        </is>
+      </c>
+      <c r="B705" s="2" t="inlineStr">
+        <is>
+          <t>Vero Do Brasil Industria E Comercio Eireli</t>
+        </is>
+      </c>
+      <c r="C705" s="2" t="inlineStr">
+        <is>
+          <t>121831</t>
+        </is>
+      </c>
+      <c r="D705" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E705" s="2" t="inlineStr">
+        <is>
+          <t>Americanópolis</t>
+        </is>
+      </c>
+      <c r="F705" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G705" s="2" t="inlineStr">
+        <is>
+          <t>84 Rua Jacinto Paes</t>
+        </is>
+      </c>
+      <c r="H705" s="2" t="inlineStr">
+        <is>
+          <t>04338-090</t>
+        </is>
+      </c>
+      <c r="I705" s="2" t="inlineStr">
+        <is>
+          <t>https://www.verodobrasil.com.br</t>
+        </is>
+      </c>
+      <c r="J705" s="2" t="inlineStr"/>
+      <c r="K705" s="2" t="inlineStr"/>
+      <c r="L705" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M705" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N705" s="2" t="inlineStr">
+        <is>
+          <t>atendimento@verodobrasil.com.br</t>
+        </is>
+      </c>
+      <c r="O705" s="2" t="inlineStr">
+        <is>
+          <t>+55 11 5622-8000</t>
+        </is>
+      </c>
+      <c r="P705" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q705" s="2" t="inlineStr">
+        <is>
+          <t>04290436000113</t>
+        </is>
+      </c>
+      <c r="R705" s="2" t="inlineStr"/>
+      <c r="S705" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/verodobrasil/</t>
+        </is>
+      </c>
+      <c r="T705" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/verodobrasil/</t>
+        </is>
+      </c>
+      <c r="U705" s="2" t="inlineStr"/>
+      <c r="V705" s="2" t="inlineStr"/>
+      <c r="W705" s="2" t="inlineStr"/>
+      <c r="X705" s="2" t="inlineStr"/>
+      <c r="Y705" s="2" t="inlineStr"/>
+      <c r="Z705" s="2" t="inlineStr"/>
+      <c r="AA705" s="2" t="inlineStr"/>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="inlineStr">
+        <is>
+          <t>Rede Super</t>
+        </is>
+      </c>
+      <c r="B706" s="2" t="inlineStr">
+        <is>
+          <t>Rede Super</t>
+        </is>
+      </c>
+      <c r="C706" s="2" t="inlineStr">
+        <is>
+          <t>87072</t>
+        </is>
+      </c>
+      <c r="D706" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E706" s="2" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F706" s="2" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Santana do Livramento</t>
+        </is>
+      </c>
+      <c r="G706" s="2" t="inlineStr">
+        <is>
+          <t>20 Avenida Tamandaré</t>
+        </is>
+      </c>
+      <c r="H706" s="2" t="inlineStr">
+        <is>
+          <t>97573-520</t>
+        </is>
+      </c>
+      <c r="I706" s="2" t="inlineStr">
+        <is>
+          <t>https://lojas.redesuper.com, https://redesuper.com</t>
+        </is>
+      </c>
+      <c r="J706" s="2" t="inlineStr"/>
+      <c r="K706" s="2" t="inlineStr"/>
+      <c r="L706" s="2" t="inlineStr"/>
+      <c r="M706" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N706" s="2" t="inlineStr">
+        <is>
+          <t>pedidos2@redesuper.com</t>
+        </is>
+      </c>
+      <c r="O706" s="2" t="inlineStr">
+        <is>
+          <t>+55 800 51 7489</t>
+        </is>
+      </c>
+      <c r="P706" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q706" s="2" t="inlineStr"/>
+      <c r="R706" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/redesuperrs/</t>
+        </is>
+      </c>
+      <c r="S706" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/redesuperrs</t>
+        </is>
+      </c>
+      <c r="T706" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redesuperrs</t>
+        </is>
+      </c>
+      <c r="U706" s="2" t="inlineStr"/>
+      <c r="V706" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redesuper9895</t>
+        </is>
+      </c>
+      <c r="W706" s="2" t="inlineStr">
+        <is>
+          <t>Franciele Turra</t>
+        </is>
+      </c>
+      <c r="X706" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y706" s="2" t="inlineStr"/>
+      <c r="Z706" s="2" t="inlineStr"/>
+      <c r="AA706" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/franciele-turra-49592283/</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="inlineStr">
+        <is>
+          <t>Rede Super</t>
+        </is>
+      </c>
+      <c r="B707" s="2" t="inlineStr">
+        <is>
+          <t>Rede Super</t>
+        </is>
+      </c>
+      <c r="C707" s="2" t="inlineStr">
+        <is>
+          <t>87072</t>
+        </is>
+      </c>
+      <c r="D707" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E707" s="2" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F707" s="2" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Santana do Livramento</t>
+        </is>
+      </c>
+      <c r="G707" s="2" t="inlineStr">
+        <is>
+          <t>20 Avenida Tamandaré</t>
+        </is>
+      </c>
+      <c r="H707" s="2" t="inlineStr">
+        <is>
+          <t>97573-520</t>
+        </is>
+      </c>
+      <c r="I707" s="2" t="inlineStr">
+        <is>
+          <t>https://lojas.redesuper.com, https://redesuper.com</t>
+        </is>
+      </c>
+      <c r="J707" s="2" t="inlineStr"/>
+      <c r="K707" s="2" t="inlineStr"/>
+      <c r="L707" s="2" t="inlineStr"/>
+      <c r="M707" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N707" s="2" t="inlineStr">
+        <is>
+          <t>pedidos2@redesuper.com</t>
+        </is>
+      </c>
+      <c r="O707" s="2" t="inlineStr">
+        <is>
+          <t>+55 800 51 7489</t>
+        </is>
+      </c>
+      <c r="P707" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q707" s="2" t="inlineStr"/>
+      <c r="R707" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/redesuperrs/</t>
+        </is>
+      </c>
+      <c r="S707" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/redesuperrs</t>
+        </is>
+      </c>
+      <c r="T707" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redesuperrs</t>
+        </is>
+      </c>
+      <c r="U707" s="2" t="inlineStr"/>
+      <c r="V707" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redesuper9895</t>
+        </is>
+      </c>
+      <c r="W707" s="2" t="inlineStr">
+        <is>
+          <t>Renato Cemin</t>
+        </is>
+      </c>
+      <c r="X707" s="2" t="inlineStr">
+        <is>
+          <t>Store Manager</t>
+        </is>
+      </c>
+      <c r="Y707" s="2" t="inlineStr"/>
+      <c r="Z707" s="2" t="inlineStr"/>
+      <c r="AA707" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/renato-cemin-5639911b4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="inlineStr">
+        <is>
+          <t>Recofran Filial 1</t>
+        </is>
+      </c>
+      <c r="B708" s="2" t="inlineStr">
+        <is>
+          <t>Recofran Filial 1</t>
+        </is>
+      </c>
+      <c r="C708" s="2" t="inlineStr">
+        <is>
+          <t>86956</t>
+        </is>
+      </c>
+      <c r="D708" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E708" s="2" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F708" s="2" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Santana do Livramento</t>
+        </is>
+      </c>
+      <c r="G708" s="2" t="inlineStr">
+        <is>
+          <t>700 Avenida Francisco Reverbel de Araújo Góes</t>
+        </is>
+      </c>
+      <c r="H708" s="2" t="inlineStr">
+        <is>
+          <t>97574-760</t>
+        </is>
+      </c>
+      <c r="I708" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recofran.com</t>
+        </is>
+      </c>
+      <c r="J708" s="2" t="inlineStr"/>
+      <c r="K708" s="2" t="inlineStr"/>
+      <c r="L708" s="2" t="inlineStr"/>
+      <c r="M708" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N708" s="2" t="inlineStr">
+        <is>
+          <t>marketing@recofran.com.br</t>
+        </is>
+      </c>
+      <c r="O708" s="2" t="inlineStr">
+        <is>
+          <t>+55 55 3243-2121</t>
+        </is>
+      </c>
+      <c r="P708" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q708" s="2" t="inlineStr"/>
+      <c r="R708" s="2" t="inlineStr"/>
+      <c r="S708" s="2" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/recofran</t>
+        </is>
+      </c>
+      <c r="T708" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/recofrandelicia</t>
+        </is>
+      </c>
+      <c r="U708" s="2" t="inlineStr"/>
+      <c r="V708" s="2" t="inlineStr"/>
+      <c r="W708" s="2" t="inlineStr"/>
+      <c r="X708" s="2" t="inlineStr"/>
+      <c r="Y708" s="2" t="inlineStr"/>
+      <c r="Z708" s="2" t="inlineStr"/>
+      <c r="AA708" s="2" t="inlineStr"/>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B709" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C709" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="D709" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E709" s="2" t="inlineStr">
+        <is>
+          <t>Porto Belo</t>
+        </is>
+      </c>
+      <c r="F709" s="2" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="G709" s="2" t="inlineStr">
+        <is>
+          <t>Rod. Br 101, S/n Km 156,5 Sala 01</t>
+        </is>
+      </c>
+      <c r="H709" s="2" t="inlineStr">
+        <is>
+          <t>88210-000</t>
+        </is>
+      </c>
+      <c r="I709" s="2" t="inlineStr">
+        <is>
+          <t>https://super.angeloni.com.br, https://www.angeloni.com.br, https://www.divvino.com.br</t>
+        </is>
+      </c>
+      <c r="J709" s="2" t="inlineStr"/>
+      <c r="K709" s="2" t="inlineStr"/>
+      <c r="L709" s="2" t="inlineStr"/>
+      <c r="M709" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N709" s="2" t="inlineStr">
+        <is>
+          <t>atendimento@angeloni.com.br</t>
+        </is>
+      </c>
+      <c r="O709" s="2" t="inlineStr">
+        <is>
+          <t>+55 48 4042-0348</t>
+        </is>
+      </c>
+      <c r="P709" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q709" s="2" t="inlineStr"/>
+      <c r="R709" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/angeloni/</t>
+        </is>
+      </c>
+      <c r="S709" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RedeAngeloni/</t>
+        </is>
+      </c>
+      <c r="T709" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redeangeloni/</t>
+        </is>
+      </c>
+      <c r="U709" s="2" t="inlineStr"/>
+      <c r="V709" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redeangeloni/</t>
+        </is>
+      </c>
+      <c r="W709" s="2" t="inlineStr">
+        <is>
+          <t>Lucas Dahmer Mattos</t>
+        </is>
+      </c>
+      <c r="X709" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y709" s="2" t="inlineStr"/>
+      <c r="Z709" s="2" t="inlineStr"/>
+      <c r="AA709" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lucas-dahmer-mattos-4b17988b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B710" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C710" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="D710" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E710" s="2" t="inlineStr">
+        <is>
+          <t>Porto Belo</t>
+        </is>
+      </c>
+      <c r="F710" s="2" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="G710" s="2" t="inlineStr">
+        <is>
+          <t>Rod. Br 101, S/n Km 156,5 Sala 01</t>
+        </is>
+      </c>
+      <c r="H710" s="2" t="inlineStr">
+        <is>
+          <t>88210-000</t>
+        </is>
+      </c>
+      <c r="I710" s="2" t="inlineStr">
+        <is>
+          <t>https://super.angeloni.com.br, https://www.angeloni.com.br, https://www.divvino.com.br</t>
+        </is>
+      </c>
+      <c r="J710" s="2" t="inlineStr"/>
+      <c r="K710" s="2" t="inlineStr"/>
+      <c r="L710" s="2" t="inlineStr"/>
+      <c r="M710" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N710" s="2" t="inlineStr">
+        <is>
+          <t>atendimento@angeloni.com.br</t>
+        </is>
+      </c>
+      <c r="O710" s="2" t="inlineStr">
+        <is>
+          <t>+55 48 4042-0348</t>
+        </is>
+      </c>
+      <c r="P710" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q710" s="2" t="inlineStr"/>
+      <c r="R710" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/angeloni/</t>
+        </is>
+      </c>
+      <c r="S710" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RedeAngeloni/</t>
+        </is>
+      </c>
+      <c r="T710" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redeangeloni/</t>
+        </is>
+      </c>
+      <c r="U710" s="2" t="inlineStr"/>
+      <c r="V710" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redeangeloni/</t>
+        </is>
+      </c>
+      <c r="W710" s="2" t="inlineStr">
+        <is>
+          <t>Rubia de Oliveira</t>
+        </is>
+      </c>
+      <c r="X710" s="2" t="inlineStr">
+        <is>
+          <t>International Business Manager</t>
+        </is>
+      </c>
+      <c r="Y710" s="2" t="inlineStr"/>
+      <c r="Z710" s="2" t="inlineStr"/>
+      <c r="AA710" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rubiaoliveiras/</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B711" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C711" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="D711" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E711" s="2" t="inlineStr">
+        <is>
+          <t>Porto Belo</t>
+        </is>
+      </c>
+      <c r="F711" s="2" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="G711" s="2" t="inlineStr">
+        <is>
+          <t>Rod. Br 101, S/n Km 156,5 Sala 01</t>
+        </is>
+      </c>
+      <c r="H711" s="2" t="inlineStr">
+        <is>
+          <t>88210-000</t>
+        </is>
+      </c>
+      <c r="I711" s="2" t="inlineStr">
+        <is>
+          <t>https://super.angeloni.com.br, https://www.angeloni.com.br, https://www.divvino.com.br</t>
+        </is>
+      </c>
+      <c r="J711" s="2" t="inlineStr"/>
+      <c r="K711" s="2" t="inlineStr"/>
+      <c r="L711" s="2" t="inlineStr"/>
+      <c r="M711" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N711" s="2" t="inlineStr">
+        <is>
+          <t>atendimento@angeloni.com.br</t>
+        </is>
+      </c>
+      <c r="O711" s="2" t="inlineStr">
+        <is>
+          <t>+55 48 4042-0348</t>
+        </is>
+      </c>
+      <c r="P711" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q711" s="2" t="inlineStr"/>
+      <c r="R711" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/angeloni/</t>
+        </is>
+      </c>
+      <c r="S711" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RedeAngeloni/</t>
+        </is>
+      </c>
+      <c r="T711" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redeangeloni/</t>
+        </is>
+      </c>
+      <c r="U711" s="2" t="inlineStr"/>
+      <c r="V711" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redeangeloni/</t>
+        </is>
+      </c>
+      <c r="W711" s="2" t="inlineStr">
+        <is>
+          <t>Vanessa Schneider</t>
+        </is>
+      </c>
+      <c r="X711" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y711" s="2" t="inlineStr"/>
+      <c r="Z711" s="2" t="inlineStr"/>
+      <c r="AA711" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vanessa-schneider-738846131/</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B712" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C712" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="D712" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E712" s="2" t="inlineStr">
+        <is>
+          <t>Porto Belo</t>
+        </is>
+      </c>
+      <c r="F712" s="2" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="G712" s="2" t="inlineStr">
+        <is>
+          <t>Rod. Br 101, S/n Km 156,5 Sala 01</t>
+        </is>
+      </c>
+      <c r="H712" s="2" t="inlineStr">
+        <is>
+          <t>88210-000</t>
+        </is>
+      </c>
+      <c r="I712" s="2" t="inlineStr">
+        <is>
+          <t>https://super.angeloni.com.br, https://www.angeloni.com.br, https://www.divvino.com.br</t>
+        </is>
+      </c>
+      <c r="J712" s="2" t="inlineStr"/>
+      <c r="K712" s="2" t="inlineStr"/>
+      <c r="L712" s="2" t="inlineStr"/>
+      <c r="M712" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N712" s="2" t="inlineStr">
+        <is>
+          <t>atendimento@angeloni.com.br</t>
+        </is>
+      </c>
+      <c r="O712" s="2" t="inlineStr">
+        <is>
+          <t>+55 48 4042-0348</t>
+        </is>
+      </c>
+      <c r="P712" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q712" s="2" t="inlineStr"/>
+      <c r="R712" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/angeloni/</t>
+        </is>
+      </c>
+      <c r="S712" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RedeAngeloni/</t>
+        </is>
+      </c>
+      <c r="T712" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redeangeloni/</t>
+        </is>
+      </c>
+      <c r="U712" s="2" t="inlineStr"/>
+      <c r="V712" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redeangeloni/</t>
+        </is>
+      </c>
+      <c r="W712" s="2" t="inlineStr">
+        <is>
+          <t>Mario Spillere</t>
+        </is>
+      </c>
+      <c r="X712" s="2" t="inlineStr">
+        <is>
+          <t>Wine Buyer</t>
+        </is>
+      </c>
+      <c r="Y712" s="2" t="inlineStr"/>
+      <c r="Z712" s="2" t="inlineStr"/>
+      <c r="AA712" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mario-spillere-028511212/</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B713" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C713" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="D713" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E713" s="2" t="inlineStr">
+        <is>
+          <t>Porto Belo</t>
+        </is>
+      </c>
+      <c r="F713" s="2" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="G713" s="2" t="inlineStr">
+        <is>
+          <t>Rod. Br 101, S/n Km 156,5 Sala 01</t>
+        </is>
+      </c>
+      <c r="H713" s="2" t="inlineStr">
+        <is>
+          <t>88210-000</t>
+        </is>
+      </c>
+      <c r="I713" s="2" t="inlineStr">
+        <is>
+          <t>https://super.angeloni.com.br, https://www.angeloni.com.br, https://www.divvino.com.br</t>
+        </is>
+      </c>
+      <c r="J713" s="2" t="inlineStr"/>
+      <c r="K713" s="2" t="inlineStr"/>
+      <c r="L713" s="2" t="inlineStr"/>
+      <c r="M713" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N713" s="2" t="inlineStr">
+        <is>
+          <t>atendimento@angeloni.com.br</t>
+        </is>
+      </c>
+      <c r="O713" s="2" t="inlineStr">
+        <is>
+          <t>+55 48 4042-0348</t>
+        </is>
+      </c>
+      <c r="P713" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q713" s="2" t="inlineStr"/>
+      <c r="R713" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/angeloni/</t>
+        </is>
+      </c>
+      <c r="S713" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RedeAngeloni/</t>
+        </is>
+      </c>
+      <c r="T713" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redeangeloni/</t>
+        </is>
+      </c>
+      <c r="U713" s="2" t="inlineStr"/>
+      <c r="V713" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redeangeloni/</t>
+        </is>
+      </c>
+      <c r="W713" s="2" t="inlineStr">
+        <is>
+          <t>Andre Meurer</t>
+        </is>
+      </c>
+      <c r="X713" s="2" t="inlineStr">
+        <is>
+          <t>Wine Consultant</t>
+        </is>
+      </c>
+      <c r="Y713" s="2" t="inlineStr"/>
+      <c r="Z713" s="2" t="inlineStr"/>
+      <c r="AA713" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andre-meurer-4b94b41a1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="inlineStr">
+        <is>
+          <t>Jc Distribuicao Logistica Importacao E Exportacao De Produtos Industrializados Ltda</t>
+        </is>
+      </c>
+      <c r="B714" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JC Distribuição </t>
+        </is>
+      </c>
+      <c r="C714" s="2" t="inlineStr">
+        <is>
+          <t>121778</t>
+        </is>
+      </c>
+      <c r="D714" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E714" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Curitiba</t>
+        </is>
+      </c>
+      <c r="F714" s="2" t="inlineStr">
+        <is>
+          <t>Goiás, Goiânia</t>
+        </is>
+      </c>
+      <c r="G714" s="2" t="inlineStr">
+        <is>
+          <t>lt 02, 2 Avenida do Povo</t>
+        </is>
+      </c>
+      <c r="H714" s="2" t="inlineStr">
+        <is>
+          <t>74480-800</t>
+        </is>
+      </c>
+      <c r="I714" s="2" t="inlineStr">
+        <is>
+          <t>https://jcdistribuicao.com.br</t>
+        </is>
+      </c>
+      <c r="J714" s="2" t="inlineStr"/>
+      <c r="K714" s="2" t="inlineStr"/>
+      <c r="L714" s="2" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="M714" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N714" s="2" t="inlineStr">
+        <is>
+          <t>lorena.ramos@jcdistribuicao.com.br</t>
+        </is>
+      </c>
+      <c r="O714" s="2" t="inlineStr">
+        <is>
+          <t>+55 62 3240-9500</t>
+        </is>
+      </c>
+      <c r="P714" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q714" s="2" t="inlineStr">
+        <is>
+          <t>06314327000114</t>
+        </is>
+      </c>
+      <c r="R714" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jc-distribui%C3%A7%C3%A3o/</t>
+        </is>
+      </c>
+      <c r="S714" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/jcdistribuicaooficial</t>
+        </is>
+      </c>
+      <c r="T714" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jcdistribuicao/</t>
+        </is>
+      </c>
+      <c r="U714" s="2" t="inlineStr"/>
+      <c r="V714" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@tvjcdistribuicao3284/</t>
+        </is>
+      </c>
+      <c r="W714" s="2" t="inlineStr">
+        <is>
+          <t>Maxsuel Marques Ferreira Costa</t>
+        </is>
+      </c>
+      <c r="X714" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y714" s="2" t="inlineStr"/>
+      <c r="Z714" s="2" t="inlineStr"/>
+      <c r="AA714" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maxsuel-marques-ferreira-costa-32a742196/</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="inlineStr">
+        <is>
+          <t>Jc Distribuicao Logistica Importacao E Exportacao De Produtos Industrializados Ltda</t>
+        </is>
+      </c>
+      <c r="B715" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JC Distribuição </t>
+        </is>
+      </c>
+      <c r="C715" s="2" t="inlineStr">
+        <is>
+          <t>121778</t>
+        </is>
+      </c>
+      <c r="D715" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E715" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Curitiba</t>
+        </is>
+      </c>
+      <c r="F715" s="2" t="inlineStr">
+        <is>
+          <t>Goiás, Goiânia</t>
+        </is>
+      </c>
+      <c r="G715" s="2" t="inlineStr">
+        <is>
+          <t>lt 02, 2 Avenida do Povo</t>
+        </is>
+      </c>
+      <c r="H715" s="2" t="inlineStr">
+        <is>
+          <t>74480-800</t>
+        </is>
+      </c>
+      <c r="I715" s="2" t="inlineStr">
+        <is>
+          <t>https://jcdistribuicao.com.br</t>
+        </is>
+      </c>
+      <c r="J715" s="2" t="inlineStr"/>
+      <c r="K715" s="2" t="inlineStr"/>
+      <c r="L715" s="2" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="M715" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N715" s="2" t="inlineStr">
+        <is>
+          <t>lorena.ramos@jcdistribuicao.com.br</t>
+        </is>
+      </c>
+      <c r="O715" s="2" t="inlineStr">
+        <is>
+          <t>+55 62 3240-9500</t>
+        </is>
+      </c>
+      <c r="P715" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q715" s="2" t="inlineStr">
+        <is>
+          <t>06314327000114</t>
+        </is>
+      </c>
+      <c r="R715" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jc-distribui%C3%A7%C3%A3o/</t>
+        </is>
+      </c>
+      <c r="S715" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/jcdistribuicaooficial</t>
+        </is>
+      </c>
+      <c r="T715" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jcdistribuicao/</t>
+        </is>
+      </c>
+      <c r="U715" s="2" t="inlineStr"/>
+      <c r="V715" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@tvjcdistribuicao3284/</t>
+        </is>
+      </c>
+      <c r="W715" s="2" t="inlineStr">
+        <is>
+          <t>Dielle Santis</t>
+        </is>
+      </c>
+      <c r="X715" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Assistant</t>
+        </is>
+      </c>
+      <c r="Y715" s="2" t="inlineStr"/>
+      <c r="Z715" s="2" t="inlineStr"/>
+      <c r="AA715" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dielle-santis-4272aa203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="inlineStr">
+        <is>
+          <t>Jc Distribuicao Logistica Importacao E Exportacao De Produtos Industrializados Ltda</t>
+        </is>
+      </c>
+      <c r="B716" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JC Distribuição </t>
+        </is>
+      </c>
+      <c r="C716" s="2" t="inlineStr">
+        <is>
+          <t>121778</t>
+        </is>
+      </c>
+      <c r="D716" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E716" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Curitiba</t>
+        </is>
+      </c>
+      <c r="F716" s="2" t="inlineStr">
+        <is>
+          <t>Goiás, Goiânia</t>
+        </is>
+      </c>
+      <c r="G716" s="2" t="inlineStr">
+        <is>
+          <t>lt 02, 2 Avenida do Povo</t>
+        </is>
+      </c>
+      <c r="H716" s="2" t="inlineStr">
+        <is>
+          <t>74480-800</t>
+        </is>
+      </c>
+      <c r="I716" s="2" t="inlineStr">
+        <is>
+          <t>https://jcdistribuicao.com.br</t>
+        </is>
+      </c>
+      <c r="J716" s="2" t="inlineStr"/>
+      <c r="K716" s="2" t="inlineStr"/>
+      <c r="L716" s="2" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="M716" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N716" s="2" t="inlineStr">
+        <is>
+          <t>lorena.ramos@jcdistribuicao.com.br</t>
+        </is>
+      </c>
+      <c r="O716" s="2" t="inlineStr">
+        <is>
+          <t>+55 62 3240-9500</t>
+        </is>
+      </c>
+      <c r="P716" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q716" s="2" t="inlineStr">
+        <is>
+          <t>06314327000114</t>
+        </is>
+      </c>
+      <c r="R716" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jc-distribui%C3%A7%C3%A3o/</t>
+        </is>
+      </c>
+      <c r="S716" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/jcdistribuicaooficial</t>
+        </is>
+      </c>
+      <c r="T716" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jcdistribuicao/</t>
+        </is>
+      </c>
+      <c r="U716" s="2" t="inlineStr"/>
+      <c r="V716" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@tvjcdistribuicao3284/</t>
+        </is>
+      </c>
+      <c r="W716" s="2" t="inlineStr">
+        <is>
+          <t>Lorena Cerqueira</t>
+        </is>
+      </c>
+      <c r="X716" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Assistant</t>
+        </is>
+      </c>
+      <c r="Y716" s="2" t="inlineStr"/>
+      <c r="Z716" s="2" t="inlineStr"/>
+      <c r="AA716" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lorena-cerqueira-ramos-62901b148/</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="inlineStr">
+        <is>
+          <t>Wine Out</t>
+        </is>
+      </c>
+      <c r="B717" s="2" t="inlineStr">
+        <is>
+          <t>Wine Out</t>
+        </is>
+      </c>
+      <c r="C717" s="2" t="inlineStr">
+        <is>
+          <t>97173</t>
+        </is>
+      </c>
+      <c r="D717" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E717" s="2" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F717" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Guarulhos</t>
+        </is>
+      </c>
+      <c r="G717" s="2" t="inlineStr">
+        <is>
+          <t>90 Rua Quinze de Novembro</t>
+        </is>
+      </c>
+      <c r="H717" s="2" t="inlineStr">
+        <is>
+          <t>07011-030</t>
+        </is>
+      </c>
+      <c r="I717" s="2" t="inlineStr">
+        <is>
+          <t>https://wineout.com.br</t>
+        </is>
+      </c>
+      <c r="J717" s="2" t="inlineStr"/>
+      <c r="K717" s="2" t="inlineStr"/>
+      <c r="L717" s="2" t="inlineStr"/>
+      <c r="M717" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N717" s="2" t="inlineStr">
+        <is>
+          <t>adm@wineout.com.br</t>
+        </is>
+      </c>
+      <c r="O717" s="2" t="inlineStr">
+        <is>
+          <t>+55 21 3827-0329</t>
+        </is>
+      </c>
+      <c r="P717" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q717" s="2" t="inlineStr"/>
+      <c r="R717" s="2" t="inlineStr"/>
+      <c r="S717" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineoutdistribuidora/</t>
+        </is>
+      </c>
+      <c r="T717" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineout_distribuidora/</t>
+        </is>
+      </c>
+      <c r="U717" s="2" t="inlineStr"/>
+      <c r="V717" s="2" t="inlineStr"/>
+      <c r="W717" s="2" t="inlineStr"/>
+      <c r="X717" s="2" t="inlineStr"/>
+      <c r="Y717" s="2" t="inlineStr"/>
+      <c r="Z717" s="2" t="inlineStr"/>
+      <c r="AA717" s="2" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="inlineStr">
+        <is>
+          <t>Megga Distribuidora Ltda</t>
+        </is>
+      </c>
+      <c r="B718" s="2" t="inlineStr"/>
+      <c r="C718" s="2" t="inlineStr">
+        <is>
+          <t>164233</t>
+        </is>
+      </c>
+      <c r="D718" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E718" s="2" t="inlineStr">
+        <is>
+          <t>Propriá</t>
+        </is>
+      </c>
+      <c r="F718" s="2" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="G718" s="2" t="inlineStr">
+        <is>
+          <t>1328 Rua Jessé Ferreira Trindade</t>
+        </is>
+      </c>
+      <c r="H718" s="2" t="inlineStr">
+        <is>
+          <t>49900-000</t>
+        </is>
+      </c>
+      <c r="I718" s="2" t="inlineStr">
+        <is>
+          <t>https://www.meggadistribuidora.com.br</t>
+        </is>
+      </c>
+      <c r="J718" s="2" t="inlineStr"/>
+      <c r="K718" s="2" t="inlineStr"/>
+      <c r="L718" s="2" t="inlineStr"/>
+      <c r="M718" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N718" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce@meggadistribuidora.com.br</t>
+        </is>
+      </c>
+      <c r="O718" s="2" t="inlineStr"/>
+      <c r="P718" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q718" s="2" t="inlineStr"/>
+      <c r="R718" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/grupomegga</t>
+        </is>
+      </c>
+      <c r="S718" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/meggadistribuidorase/</t>
+        </is>
+      </c>
+      <c r="T718" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/meggadistribuidorase/</t>
+        </is>
+      </c>
+      <c r="U718" s="2" t="inlineStr"/>
+      <c r="V718" s="2" t="inlineStr"/>
+      <c r="W718" s="2" t="inlineStr">
+        <is>
+          <t>Valdson Nunes</t>
+        </is>
+      </c>
+      <c r="X718" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y718" s="2" t="inlineStr"/>
+      <c r="Z718" s="2" t="inlineStr"/>
+      <c r="AA718" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/valdson-nunes-327a12103/</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="inlineStr">
+        <is>
+          <t>Megga Distribuidora Ltda</t>
+        </is>
+      </c>
+      <c r="B719" s="2" t="inlineStr"/>
+      <c r="C719" s="2" t="inlineStr">
+        <is>
+          <t>164233</t>
+        </is>
+      </c>
+      <c r="D719" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E719" s="2" t="inlineStr">
+        <is>
+          <t>Propriá</t>
+        </is>
+      </c>
+      <c r="F719" s="2" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="G719" s="2" t="inlineStr">
+        <is>
+          <t>1328 Rua Jessé Ferreira Trindade</t>
+        </is>
+      </c>
+      <c r="H719" s="2" t="inlineStr">
+        <is>
+          <t>49900-000</t>
+        </is>
+      </c>
+      <c r="I719" s="2" t="inlineStr">
+        <is>
+          <t>https://www.meggadistribuidora.com.br</t>
+        </is>
+      </c>
+      <c r="J719" s="2" t="inlineStr"/>
+      <c r="K719" s="2" t="inlineStr"/>
+      <c r="L719" s="2" t="inlineStr"/>
+      <c r="M719" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N719" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce@meggadistribuidora.com.br</t>
+        </is>
+      </c>
+      <c r="O719" s="2" t="inlineStr"/>
+      <c r="P719" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q719" s="2" t="inlineStr"/>
+      <c r="R719" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/grupomegga</t>
+        </is>
+      </c>
+      <c r="S719" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/meggadistribuidorase/</t>
+        </is>
+      </c>
+      <c r="T719" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/meggadistribuidorase/</t>
+        </is>
+      </c>
+      <c r="U719" s="2" t="inlineStr"/>
+      <c r="V719" s="2" t="inlineStr"/>
+      <c r="W719" s="2" t="inlineStr">
+        <is>
+          <t>Claudio Martins</t>
+        </is>
+      </c>
+      <c r="X719" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y719" s="2" t="inlineStr"/>
+      <c r="Z719" s="2" t="inlineStr"/>
+      <c r="AA719" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/claudio-martins-3a83aa161/</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="inlineStr">
+        <is>
+          <t>Nova Mega G Atacadista De Alimentos Sa</t>
+        </is>
+      </c>
+      <c r="B720" s="2" t="inlineStr"/>
+      <c r="C720" s="2" t="inlineStr">
+        <is>
+          <t>164232</t>
+        </is>
+      </c>
+      <c r="D720" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E720" s="2" t="inlineStr">
+        <is>
+          <t>Jardim São Luís</t>
+        </is>
+      </c>
+      <c r="F720" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G720" s="2" t="inlineStr">
+        <is>
+          <t>573 Avenida Maria Coelho Aguiar</t>
+        </is>
+      </c>
+      <c r="H720" s="2" t="inlineStr">
+        <is>
+          <t>05813-040</t>
+        </is>
+      </c>
+      <c r="I720" s="2" t="inlineStr">
+        <is>
+          <t>https://megag.com.br</t>
+        </is>
+      </c>
+      <c r="J720" s="2" t="inlineStr"/>
+      <c r="K720" s="2" t="inlineStr"/>
+      <c r="L720" s="2" t="inlineStr"/>
+      <c r="M720" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N720" s="2" t="inlineStr">
+        <is>
+          <t>raquel.rabelo@megag.com.br</t>
+        </is>
+      </c>
+      <c r="O720" s="2" t="inlineStr"/>
+      <c r="P720" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q720" s="2" t="inlineStr"/>
+      <c r="R720" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/megag-alimentos/</t>
+        </is>
+      </c>
+      <c r="S720" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/megag.atacadistadealimentos/</t>
+        </is>
+      </c>
+      <c r="T720" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megagalimentosoficial/</t>
+        </is>
+      </c>
+      <c r="U720" s="2" t="inlineStr"/>
+      <c r="V720" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@megagalimentosoficial/</t>
+        </is>
+      </c>
+      <c r="W720" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Rabelo</t>
+        </is>
+      </c>
+      <c r="X720" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Assistant</t>
+        </is>
+      </c>
+      <c r="Y720" s="2" t="inlineStr"/>
+      <c r="Z720" s="2" t="inlineStr"/>
+      <c r="AA720" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/raquel-rabelo-39666418a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="inlineStr">
+        <is>
+          <t>Nova Mega G Atacadista De Alimentos Sa</t>
+        </is>
+      </c>
+      <c r="B721" s="2" t="inlineStr"/>
+      <c r="C721" s="2" t="inlineStr">
+        <is>
+          <t>164232</t>
+        </is>
+      </c>
+      <c r="D721" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E721" s="2" t="inlineStr">
+        <is>
+          <t>Jardim São Luís</t>
+        </is>
+      </c>
+      <c r="F721" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G721" s="2" t="inlineStr">
+        <is>
+          <t>573 Avenida Maria Coelho Aguiar</t>
+        </is>
+      </c>
+      <c r="H721" s="2" t="inlineStr">
+        <is>
+          <t>05813-040</t>
+        </is>
+      </c>
+      <c r="I721" s="2" t="inlineStr">
+        <is>
+          <t>https://megag.com.br</t>
+        </is>
+      </c>
+      <c r="J721" s="2" t="inlineStr"/>
+      <c r="K721" s="2" t="inlineStr"/>
+      <c r="L721" s="2" t="inlineStr"/>
+      <c r="M721" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N721" s="2" t="inlineStr">
+        <is>
+          <t>raquel.rabelo@megag.com.br</t>
+        </is>
+      </c>
+      <c r="O721" s="2" t="inlineStr"/>
+      <c r="P721" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q721" s="2" t="inlineStr"/>
+      <c r="R721" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/megag-alimentos/</t>
+        </is>
+      </c>
+      <c r="S721" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/megag.atacadistadealimentos/</t>
+        </is>
+      </c>
+      <c r="T721" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megagalimentosoficial/</t>
+        </is>
+      </c>
+      <c r="U721" s="2" t="inlineStr"/>
+      <c r="V721" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@megagalimentosoficial/</t>
+        </is>
+      </c>
+      <c r="W721" s="2" t="inlineStr">
+        <is>
+          <t>Thalita Costa</t>
+        </is>
+      </c>
+      <c r="X721" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Assistant</t>
+        </is>
+      </c>
+      <c r="Y721" s="2" t="inlineStr"/>
+      <c r="Z721" s="2" t="inlineStr"/>
+      <c r="AA721" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thalita-costa-232b8517b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="inlineStr">
+        <is>
+          <t>Adega Franco Comercio De Bebidas Eireli</t>
+        </is>
+      </c>
+      <c r="B722" s="2" t="inlineStr">
+        <is>
+          <t>Adega Franco Comercio De Bebidas Eireli</t>
+        </is>
+      </c>
+      <c r="C722" s="2" t="inlineStr">
+        <is>
+          <t>59381</t>
+        </is>
+      </c>
+      <c r="D722" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E722" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Lange</t>
+        </is>
+      </c>
+      <c r="F722" s="2" t="inlineStr">
+        <is>
+          <t>Paraná, Curitiba</t>
+        </is>
+      </c>
+      <c r="G722" s="2" t="inlineStr">
+        <is>
+          <t>1320 Rua Augusto Stresser</t>
+        </is>
+      </c>
+      <c r="H722" s="2" t="inlineStr">
+        <is>
+          <t>80040-310</t>
+        </is>
+      </c>
+      <c r="I722" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adegafranco.com.br</t>
+        </is>
+      </c>
+      <c r="J722" s="2" t="inlineStr"/>
+      <c r="K722" s="2" t="inlineStr"/>
+      <c r="L722" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M722" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N722" s="2" t="inlineStr">
+        <is>
+          <t>guilherme@adegafranco.com.br</t>
+        </is>
+      </c>
+      <c r="O722" s="2" t="inlineStr">
+        <is>
+          <t>+55 41 3362-2265</t>
+        </is>
+      </c>
+      <c r="P722" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q722" s="2" t="inlineStr">
+        <is>
+          <t>10228713000160</t>
+        </is>
+      </c>
+      <c r="R722" s="2" t="inlineStr"/>
+      <c r="S722" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.facebook.com/aadegafrancolojadevinhos/?rf=143502249051512</t>
+        </is>
+      </c>
+      <c r="T722" s="2" t="inlineStr"/>
+      <c r="U722" s="2" t="inlineStr"/>
+      <c r="V722" s="2" t="inlineStr"/>
+      <c r="W722" s="2" t="inlineStr">
+        <is>
+          <t>Guilherme Franco</t>
+        </is>
+      </c>
+      <c r="X722" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y722" s="2" t="inlineStr"/>
+      <c r="Z722" s="2" t="inlineStr"/>
+      <c r="AA722" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/guilherme-franco-15024714/</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="inlineStr">
+        <is>
+          <t>Silva E Barbosa Comercio De Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="B723" s="2" t="inlineStr">
+        <is>
+          <t>Silva E Barbosa Comercio De Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="C723" s="2" t="inlineStr">
+        <is>
+          <t>157306</t>
+        </is>
+      </c>
+      <c r="D723" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E723" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Santa Rita</t>
+        </is>
+      </c>
+      <c r="F723" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Guarulhos</t>
+        </is>
+      </c>
+      <c r="G723" s="2" t="inlineStr">
+        <is>
+          <t>Rua Santo Antônio do Aventureiro</t>
+        </is>
+      </c>
+      <c r="H723" s="2" t="inlineStr">
+        <is>
+          <t>07143-040</t>
+        </is>
+      </c>
+      <c r="I723" s="2" t="inlineStr">
+        <is>
+          <t>https://www.barbosasupermercados.com.br</t>
+        </is>
+      </c>
+      <c r="J723" s="2" t="inlineStr"/>
+      <c r="K723" s="2" t="inlineStr"/>
+      <c r="L723" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="M723" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N723" s="2" t="inlineStr">
+        <is>
+          <t>pamela@barbosasm.com.br</t>
+        </is>
+      </c>
+      <c r="O723" s="2" t="inlineStr">
+        <is>
+          <t>+55 11 3003-2557</t>
+        </is>
+      </c>
+      <c r="P723" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q723" s="2" t="inlineStr">
+        <is>
+          <t>60437647000107</t>
+        </is>
+      </c>
+      <c r="R723" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/barbosa-supermercados/</t>
+        </is>
+      </c>
+      <c r="S723" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/barbosasm/</t>
+        </is>
+      </c>
+      <c r="T723" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barbosasupermercados/</t>
+        </is>
+      </c>
+      <c r="U723" s="2" t="inlineStr"/>
+      <c r="V723" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@barbosasupermercados6703/</t>
+        </is>
+      </c>
+      <c r="W723" s="2" t="inlineStr">
+        <is>
+          <t>Aluizio Luiz</t>
+        </is>
+      </c>
+      <c r="X723" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y723" s="2" t="inlineStr"/>
+      <c r="Z723" s="2" t="inlineStr"/>
+      <c r="AA723" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aluizio-luiz-de-almeida-8b3779177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="inlineStr">
+        <is>
+          <t>Silva E Barbosa Comercio De Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="B724" s="2" t="inlineStr">
+        <is>
+          <t>Silva E Barbosa Comercio De Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="C724" s="2" t="inlineStr">
+        <is>
+          <t>157306</t>
+        </is>
+      </c>
+      <c r="D724" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E724" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Santa Rita</t>
+        </is>
+      </c>
+      <c r="F724" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Guarulhos</t>
+        </is>
+      </c>
+      <c r="G724" s="2" t="inlineStr">
+        <is>
+          <t>Rua Santo Antônio do Aventureiro</t>
+        </is>
+      </c>
+      <c r="H724" s="2" t="inlineStr">
+        <is>
+          <t>07143-040</t>
+        </is>
+      </c>
+      <c r="I724" s="2" t="inlineStr">
+        <is>
+          <t>https://www.barbosasupermercados.com.br</t>
+        </is>
+      </c>
+      <c r="J724" s="2" t="inlineStr"/>
+      <c r="K724" s="2" t="inlineStr"/>
+      <c r="L724" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="M724" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N724" s="2" t="inlineStr">
+        <is>
+          <t>pamela@barbosasm.com.br</t>
+        </is>
+      </c>
+      <c r="O724" s="2" t="inlineStr">
+        <is>
+          <t>+55 11 3003-2557</t>
+        </is>
+      </c>
+      <c r="P724" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q724" s="2" t="inlineStr">
+        <is>
+          <t>60437647000107</t>
+        </is>
+      </c>
+      <c r="R724" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/barbosa-supermercados/</t>
+        </is>
+      </c>
+      <c r="S724" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/barbosasm/</t>
+        </is>
+      </c>
+      <c r="T724" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barbosasupermercados/</t>
+        </is>
+      </c>
+      <c r="U724" s="2" t="inlineStr"/>
+      <c r="V724" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@barbosasupermercados6703/</t>
+        </is>
+      </c>
+      <c r="W724" s="2" t="inlineStr">
+        <is>
+          <t>Augusto Navajas</t>
+        </is>
+      </c>
+      <c r="X724" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y724" s="2" t="inlineStr"/>
+      <c r="Z724" s="2" t="inlineStr"/>
+      <c r="AA724" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/augusto-navajas-878134b6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="inlineStr">
+        <is>
+          <t>Silva E Barbosa Comercio De Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="B725" s="2" t="inlineStr">
+        <is>
+          <t>Silva E Barbosa Comercio De Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="C725" s="2" t="inlineStr">
+        <is>
+          <t>157306</t>
+        </is>
+      </c>
+      <c r="D725" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E725" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Santa Rita</t>
+        </is>
+      </c>
+      <c r="F725" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Guarulhos</t>
+        </is>
+      </c>
+      <c r="G725" s="2" t="inlineStr">
+        <is>
+          <t>Rua Santo Antônio do Aventureiro</t>
+        </is>
+      </c>
+      <c r="H725" s="2" t="inlineStr">
+        <is>
+          <t>07143-040</t>
+        </is>
+      </c>
+      <c r="I725" s="2" t="inlineStr">
+        <is>
+          <t>https://www.barbosasupermercados.com.br</t>
+        </is>
+      </c>
+      <c r="J725" s="2" t="inlineStr"/>
+      <c r="K725" s="2" t="inlineStr"/>
+      <c r="L725" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="M725" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N725" s="2" t="inlineStr">
+        <is>
+          <t>pamela@barbosasm.com.br</t>
+        </is>
+      </c>
+      <c r="O725" s="2" t="inlineStr">
+        <is>
+          <t>+55 11 3003-2557</t>
+        </is>
+      </c>
+      <c r="P725" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q725" s="2" t="inlineStr">
+        <is>
+          <t>60437647000107</t>
+        </is>
+      </c>
+      <c r="R725" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/barbosa-supermercados/</t>
+        </is>
+      </c>
+      <c r="S725" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/barbosasm/</t>
+        </is>
+      </c>
+      <c r="T725" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barbosasupermercados/</t>
+        </is>
+      </c>
+      <c r="U725" s="2" t="inlineStr"/>
+      <c r="V725" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@barbosasupermercados6703/</t>
+        </is>
+      </c>
+      <c r="W725" s="2" t="inlineStr">
+        <is>
+          <t>Pamela Cristina</t>
+        </is>
+      </c>
+      <c r="X725" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y725" s="2" t="inlineStr"/>
+      <c r="Z725" s="2" t="inlineStr"/>
+      <c r="AA725" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pamela-cristina-229463223/</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="inlineStr">
+        <is>
+          <t>Brindisi Vinhos Comércio De Bebidas Ltda.</t>
+        </is>
+      </c>
+      <c r="B726" s="2" t="inlineStr">
+        <is>
+          <t>Brindisi Vinhos Comércio De Bebidas Ltda.</t>
+        </is>
+      </c>
+      <c r="C726" s="2" t="inlineStr">
+        <is>
+          <t>50932</t>
+        </is>
+      </c>
+      <c r="D726" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E726" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Paulistano</t>
+        </is>
+      </c>
+      <c r="F726" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G726" s="2" t="inlineStr">
+        <is>
+          <t>187 Loja2 Rua Professor Artur Ramos</t>
+        </is>
+      </c>
+      <c r="H726" s="2" t="inlineStr">
+        <is>
+          <t>01454-011</t>
+        </is>
+      </c>
+      <c r="I726" s="2" t="inlineStr">
+        <is>
+          <t>https://brindisivinhos.com.br</t>
+        </is>
+      </c>
+      <c r="J726" s="2" t="inlineStr"/>
+      <c r="K726" s="2" t="inlineStr"/>
+      <c r="L726" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M726" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N726" s="2" t="inlineStr">
+        <is>
+          <t>sac@brindisivinhos.com.br</t>
+        </is>
+      </c>
+      <c r="O726" s="2" t="inlineStr"/>
+      <c r="P726" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q726" s="2" t="inlineStr">
+        <is>
+          <t>31139452000182</t>
+        </is>
+      </c>
+      <c r="R726" s="2" t="inlineStr"/>
+      <c r="S726" s="2" t="inlineStr"/>
+      <c r="T726" s="2" t="inlineStr"/>
+      <c r="U726" s="2" t="inlineStr"/>
+      <c r="V726" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/BrindisiVinhos</t>
+        </is>
+      </c>
+      <c r="W726" s="2" t="inlineStr">
+        <is>
+          <t>Luiz fernando</t>
+        </is>
+      </c>
+      <c r="X726" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y726" s="2" t="inlineStr"/>
+      <c r="Z726" s="2" t="inlineStr"/>
+      <c r="AA726" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luiz-fernando-de-almeida-lima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="2" t="inlineStr">
+        <is>
+          <t>Brindisi Vinhos Comércio De Bebidas Ltda.</t>
+        </is>
+      </c>
+      <c r="B727" s="2" t="inlineStr">
+        <is>
+          <t>Brindisi Vinhos Comércio De Bebidas Ltda.</t>
+        </is>
+      </c>
+      <c r="C727" s="2" t="inlineStr">
+        <is>
+          <t>50932</t>
+        </is>
+      </c>
+      <c r="D727" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E727" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Paulistano</t>
+        </is>
+      </c>
+      <c r="F727" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G727" s="2" t="inlineStr">
+        <is>
+          <t>187 Loja2 Rua Professor Artur Ramos</t>
+        </is>
+      </c>
+      <c r="H727" s="2" t="inlineStr">
+        <is>
+          <t>01454-011</t>
+        </is>
+      </c>
+      <c r="I727" s="2" t="inlineStr">
+        <is>
+          <t>https://brindisivinhos.com.br</t>
+        </is>
+      </c>
+      <c r="J727" s="2" t="inlineStr"/>
+      <c r="K727" s="2" t="inlineStr"/>
+      <c r="L727" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M727" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N727" s="2" t="inlineStr">
+        <is>
+          <t>sac@brindisivinhos.com.br</t>
+        </is>
+      </c>
+      <c r="O727" s="2" t="inlineStr"/>
+      <c r="P727" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q727" s="2" t="inlineStr">
+        <is>
+          <t>31139452000182</t>
+        </is>
+      </c>
+      <c r="R727" s="2" t="inlineStr"/>
+      <c r="S727" s="2" t="inlineStr"/>
+      <c r="T727" s="2" t="inlineStr"/>
+      <c r="U727" s="2" t="inlineStr"/>
+      <c r="V727" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/BrindisiVinhos</t>
+        </is>
+      </c>
+      <c r="W727" s="2" t="inlineStr">
+        <is>
+          <t>Ana Carla</t>
+        </is>
+      </c>
+      <c r="X727" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y727" s="2" t="inlineStr"/>
+      <c r="Z727" s="2" t="inlineStr"/>
+      <c r="AA727" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ana-carla-moraes-de-oliveira-74a03229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="inlineStr">
+        <is>
+          <t>L.s.a. Correa - Vinhos</t>
+        </is>
+      </c>
+      <c r="B728" s="2" t="inlineStr">
+        <is>
+          <t>L.s.a. Correa - Vinhos</t>
+        </is>
+      </c>
+      <c r="C728" s="2" t="inlineStr">
+        <is>
+          <t>111910</t>
+        </is>
+      </c>
+      <c r="D728" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E728" s="2" t="inlineStr">
+        <is>
+          <t>Gonzaga</t>
+        </is>
+      </c>
+      <c r="F728" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Santos</t>
+        </is>
+      </c>
+      <c r="G728" s="2" t="inlineStr">
+        <is>
+          <t>59 Avenida Ana Costa</t>
+        </is>
+      </c>
+      <c r="H728" s="2" t="inlineStr">
+        <is>
+          <t>11060-001</t>
+        </is>
+      </c>
+      <c r="I728" s="2" t="inlineStr">
+        <is>
+          <t>https://wine2go.com.br</t>
+        </is>
+      </c>
+      <c r="J728" s="2" t="inlineStr"/>
+      <c r="K728" s="2" t="inlineStr"/>
+      <c r="L728" s="2" t="inlineStr"/>
+      <c r="M728" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N728" s="2" t="inlineStr">
+        <is>
+          <t>fernanda@wine2go.com.br</t>
+        </is>
+      </c>
+      <c r="O728" s="2" t="inlineStr"/>
+      <c r="P728" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q728" s="2" t="inlineStr"/>
+      <c r="R728" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine2go-brasil/</t>
+        </is>
+      </c>
+      <c r="S728" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wine2gobrasil/</t>
+        </is>
+      </c>
+      <c r="T728" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine2gobrasil</t>
+        </is>
+      </c>
+      <c r="U728" s="2" t="inlineStr"/>
+      <c r="V728" s="2" t="inlineStr"/>
+      <c r="W728" s="2" t="inlineStr">
+        <is>
+          <t>Fernanda Barreiros</t>
+        </is>
+      </c>
+      <c r="X728" s="2" t="inlineStr">
+        <is>
+          <t>Business Partner</t>
+        </is>
+      </c>
+      <c r="Y728" s="2" t="inlineStr"/>
+      <c r="Z728" s="2" t="inlineStr"/>
+      <c r="AA728" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernanda-barreiros-2b8402270/</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="inlineStr">
+        <is>
+          <t>Cmp - Comércio, Importação E Exportação De Bebidas E Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="B729" s="2" t="inlineStr">
+        <is>
+          <t>Cmp - Comércio, Importação E Exportação De Bebidas E Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="C729" s="2" t="inlineStr">
+        <is>
+          <t>40916</t>
+        </is>
+      </c>
+      <c r="D729" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E729" s="2" t="inlineStr">
+        <is>
+          <t>Itaim Bibi</t>
+        </is>
+      </c>
+      <c r="F729" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G729" s="2" t="inlineStr">
+        <is>
+          <t>162 Rua Romilda Margarida Gabriel</t>
+        </is>
+      </c>
+      <c r="H729" s="2" t="inlineStr">
+        <is>
+          <t>04530-090</t>
+        </is>
+      </c>
+      <c r="I729" s="2" t="inlineStr">
+        <is>
+          <t>https://caveleman.com</t>
+        </is>
+      </c>
+      <c r="J729" s="2" t="inlineStr"/>
+      <c r="K729" s="2" t="inlineStr"/>
+      <c r="L729" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M729" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N729" s="2" t="inlineStr">
+        <is>
+          <t>marcio.morelli@caveleman.com.br</t>
+        </is>
+      </c>
+      <c r="O729" s="2" t="inlineStr"/>
+      <c r="P729" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q729" s="2" t="inlineStr">
+        <is>
+          <t>29686483000101</t>
+        </is>
+      </c>
+      <c r="R729" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cave-leman/</t>
+        </is>
+      </c>
+      <c r="S729" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.facebook.com/caveleman/</t>
+        </is>
+      </c>
+      <c r="T729" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/caveleman</t>
+        </is>
+      </c>
+      <c r="U729" s="2" t="inlineStr"/>
+      <c r="V729" s="2" t="inlineStr"/>
+      <c r="W729" s="2" t="inlineStr">
+        <is>
+          <t>Marcio Morelli</t>
+        </is>
+      </c>
+      <c r="X729" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y729" s="2" t="inlineStr"/>
+      <c r="Z729" s="2" t="inlineStr"/>
+      <c r="AA729" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marciomorelli/</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="inlineStr">
+        <is>
+          <t>Cmp - Comércio, Importação E Exportação De Bebidas E Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="B730" s="2" t="inlineStr">
+        <is>
+          <t>Cmp - Comércio, Importação E Exportação De Bebidas E Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="C730" s="2" t="inlineStr">
+        <is>
+          <t>40916</t>
+        </is>
+      </c>
+      <c r="D730" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E730" s="2" t="inlineStr">
+        <is>
+          <t>Itaim Bibi</t>
+        </is>
+      </c>
+      <c r="F730" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G730" s="2" t="inlineStr">
+        <is>
+          <t>162 Rua Romilda Margarida Gabriel</t>
+        </is>
+      </c>
+      <c r="H730" s="2" t="inlineStr">
+        <is>
+          <t>04530-090</t>
+        </is>
+      </c>
+      <c r="I730" s="2" t="inlineStr">
+        <is>
+          <t>https://caveleman.com</t>
+        </is>
+      </c>
+      <c r="J730" s="2" t="inlineStr"/>
+      <c r="K730" s="2" t="inlineStr"/>
+      <c r="L730" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M730" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N730" s="2" t="inlineStr">
+        <is>
+          <t>marcio.morelli@caveleman.com.br</t>
+        </is>
+      </c>
+      <c r="O730" s="2" t="inlineStr"/>
+      <c r="P730" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q730" s="2" t="inlineStr">
+        <is>
+          <t>29686483000101</t>
+        </is>
+      </c>
+      <c r="R730" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cave-leman/</t>
+        </is>
+      </c>
+      <c r="S730" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.facebook.com/caveleman/</t>
+        </is>
+      </c>
+      <c r="T730" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/caveleman</t>
+        </is>
+      </c>
+      <c r="U730" s="2" t="inlineStr"/>
+      <c r="V730" s="2" t="inlineStr"/>
+      <c r="W730" s="2" t="inlineStr">
+        <is>
+          <t>Lucas Toledo</t>
+        </is>
+      </c>
+      <c r="X730" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Representative</t>
+        </is>
+      </c>
+      <c r="Y730" s="2" t="inlineStr"/>
+      <c r="Z730" s="2" t="inlineStr"/>
+      <c r="AA730" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lucas-toledo-piza-amighini-8ab139137/</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="inlineStr">
+        <is>
+          <t>Comercial De Queijos E Vinhos Batel Eireli</t>
+        </is>
+      </c>
+      <c r="B731" s="2" t="inlineStr">
+        <is>
+          <t>Comercial De Queijos E Vinhos Batel Eireli</t>
+        </is>
+      </c>
+      <c r="C731" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D731" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E731" s="2" t="inlineStr">
+        <is>
+          <t>Batel</t>
+        </is>
+      </c>
+      <c r="F731" s="2" t="inlineStr">
+        <is>
+          <t>Paraná, Curitiba</t>
+        </is>
+      </c>
+      <c r="G731" s="2" t="inlineStr">
+        <is>
+          <t>1865 Avenida Sete de Setembro</t>
+        </is>
+      </c>
+      <c r="H731" s="2" t="inlineStr">
+        <is>
+          <t>80060-070</t>
+        </is>
+      </c>
+      <c r="I731" s="2" t="inlineStr">
+        <is>
+          <t>https://adegacuritibana.com.br</t>
+        </is>
+      </c>
+      <c r="J731" s="2" t="inlineStr"/>
+      <c r="K731" s="2" t="inlineStr"/>
+      <c r="L731" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M731" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N731" s="2" t="inlineStr">
+        <is>
+          <t>sac@adegacuritibana.com.br</t>
+        </is>
+      </c>
+      <c r="O731" s="2" t="inlineStr"/>
+      <c r="P731" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q731" s="2" t="inlineStr">
+        <is>
+          <t>09025700000105</t>
+        </is>
+      </c>
+      <c r="R731" s="2" t="inlineStr"/>
+      <c r="S731" s="2" t="inlineStr"/>
+      <c r="T731" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/adegacuritibana/</t>
+        </is>
+      </c>
+      <c r="U731" s="2" t="inlineStr"/>
+      <c r="V731" s="2" t="inlineStr"/>
+      <c r="W731" s="2" t="inlineStr">
+        <is>
+          <t>Maricel Heiden</t>
+        </is>
+      </c>
+      <c r="X731" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y731" s="2" t="inlineStr"/>
+      <c r="Z731" s="2" t="inlineStr"/>
+      <c r="AA731" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maricel-heiden-235a6a5b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda</t>
+        </is>
+      </c>
+      <c r="B732" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda.</t>
+        </is>
+      </c>
+      <c r="C732" s="2" t="inlineStr">
+        <is>
+          <t>121210</t>
+        </is>
+      </c>
+      <c r="D732" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E732" s="2" t="inlineStr">
+        <is>
+          <t>Moema</t>
+        </is>
+      </c>
+      <c r="F732" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G732" s="2" t="inlineStr">
+        <is>
+          <t>60 Avenida Rouxinol</t>
+        </is>
+      </c>
+      <c r="H732" s="2" t="inlineStr">
+        <is>
+          <t>04516-000</t>
+        </is>
+      </c>
+      <c r="I732" s="2" t="inlineStr">
+        <is>
+          <t>https://www.importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="J732" s="2" t="inlineStr"/>
+      <c r="K732" s="2" t="inlineStr"/>
+      <c r="L732" s="2" t="inlineStr"/>
+      <c r="M732" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N732" s="2" t="inlineStr">
+        <is>
+          <t>patricia.martins@importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="O732" s="2" t="inlineStr">
+        <is>
+          <t>+55 47 3048-0609</t>
+        </is>
+      </c>
+      <c r="P732" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q732" s="2" t="inlineStr">
+        <is>
+          <t>24004841000135</t>
+        </is>
+      </c>
+      <c r="R732" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boena-importadora/</t>
+        </is>
+      </c>
+      <c r="S732" s="2" t="inlineStr"/>
+      <c r="T732" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boenaimportadora/</t>
+        </is>
+      </c>
+      <c r="U732" s="2" t="inlineStr"/>
+      <c r="V732" s="2" t="inlineStr"/>
+      <c r="W732" s="2" t="inlineStr">
+        <is>
+          <t>Newton Carlos</t>
+        </is>
+      </c>
+      <c r="X732" s="2" t="inlineStr">
+        <is>
+          <t>National Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y732" s="2" t="inlineStr"/>
+      <c r="Z732" s="2" t="inlineStr"/>
+      <c r="AA732" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/newton-carlos-almeida-9b40a458/</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda</t>
+        </is>
+      </c>
+      <c r="B733" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda.</t>
+        </is>
+      </c>
+      <c r="C733" s="2" t="inlineStr">
+        <is>
+          <t>121210</t>
+        </is>
+      </c>
+      <c r="D733" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E733" s="2" t="inlineStr">
+        <is>
+          <t>Moema</t>
+        </is>
+      </c>
+      <c r="F733" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G733" s="2" t="inlineStr">
+        <is>
+          <t>60 Avenida Rouxinol</t>
+        </is>
+      </c>
+      <c r="H733" s="2" t="inlineStr">
+        <is>
+          <t>04516-000</t>
+        </is>
+      </c>
+      <c r="I733" s="2" t="inlineStr">
+        <is>
+          <t>https://www.importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="J733" s="2" t="inlineStr"/>
+      <c r="K733" s="2" t="inlineStr"/>
+      <c r="L733" s="2" t="inlineStr"/>
+      <c r="M733" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N733" s="2" t="inlineStr">
+        <is>
+          <t>patricia.martins@importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="O733" s="2" t="inlineStr">
+        <is>
+          <t>+55 47 3048-0609</t>
+        </is>
+      </c>
+      <c r="P733" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q733" s="2" t="inlineStr">
+        <is>
+          <t>24004841000135</t>
+        </is>
+      </c>
+      <c r="R733" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boena-importadora/</t>
+        </is>
+      </c>
+      <c r="S733" s="2" t="inlineStr"/>
+      <c r="T733" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boenaimportadora/</t>
+        </is>
+      </c>
+      <c r="U733" s="2" t="inlineStr"/>
+      <c r="V733" s="2" t="inlineStr"/>
+      <c r="W733" s="2" t="inlineStr">
+        <is>
+          <t>Patricia F</t>
+        </is>
+      </c>
+      <c r="X733" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Manager</t>
+        </is>
+      </c>
+      <c r="Y733" s="2" t="inlineStr"/>
+      <c r="Z733" s="2" t="inlineStr"/>
+      <c r="AA733" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricia-f-martins-643a4320b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="B734" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="C734" s="2" t="inlineStr">
+        <is>
+          <t>25723</t>
+        </is>
+      </c>
+      <c r="D734" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E734" s="2" t="inlineStr">
+        <is>
+          <t>Imperial de São Cristóvão</t>
+        </is>
+      </c>
+      <c r="F734" s="2" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G734" s="2" t="inlineStr">
+        <is>
+          <t>316 Avenida Pedro II</t>
+        </is>
+      </c>
+      <c r="H734" s="2" t="inlineStr">
+        <is>
+          <t>20941-070</t>
+        </is>
+      </c>
+      <c r="I734" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lojaenoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="J734" s="2" t="inlineStr"/>
+      <c r="K734" s="2" t="inlineStr"/>
+      <c r="L734" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M734" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N734" s="2" t="inlineStr">
+        <is>
+          <t>tsalame@enoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="O734" s="2" t="inlineStr">
+        <is>
+          <t>+55 21 2042-8980</t>
+        </is>
+      </c>
+      <c r="P734" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q734" s="2" t="inlineStr">
+        <is>
+          <t>20345380000103</t>
+        </is>
+      </c>
+      <c r="R734" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enoeventos-importadora-de-bebidas-ltda-/</t>
+        </is>
+      </c>
+      <c r="S734" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="T734" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="U734" s="2" t="inlineStr"/>
+      <c r="V734" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@EnoeventosImportadora</t>
+        </is>
+      </c>
+      <c r="W734" s="2" t="inlineStr">
+        <is>
+          <t>Thiago Salame</t>
+        </is>
+      </c>
+      <c r="X734" s="2" t="inlineStr">
+        <is>
+          <t>Partner - Director</t>
+        </is>
+      </c>
+      <c r="Y734" s="2" t="inlineStr"/>
+      <c r="Z734" s="2" t="inlineStr"/>
+      <c r="AA734" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thiago-salame-b2511024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="B735" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="C735" s="2" t="inlineStr">
+        <is>
+          <t>25723</t>
+        </is>
+      </c>
+      <c r="D735" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E735" s="2" t="inlineStr">
+        <is>
+          <t>Imperial de São Cristóvão</t>
+        </is>
+      </c>
+      <c r="F735" s="2" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G735" s="2" t="inlineStr">
+        <is>
+          <t>316 Avenida Pedro II</t>
+        </is>
+      </c>
+      <c r="H735" s="2" t="inlineStr">
+        <is>
+          <t>20941-070</t>
+        </is>
+      </c>
+      <c r="I735" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lojaenoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="J735" s="2" t="inlineStr"/>
+      <c r="K735" s="2" t="inlineStr"/>
+      <c r="L735" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M735" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N735" s="2" t="inlineStr">
+        <is>
+          <t>tsalame@enoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="O735" s="2" t="inlineStr">
+        <is>
+          <t>+55 21 2042-8980</t>
+        </is>
+      </c>
+      <c r="P735" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q735" s="2" t="inlineStr">
+        <is>
+          <t>20345380000103</t>
+        </is>
+      </c>
+      <c r="R735" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enoeventos-importadora-de-bebidas-ltda-/</t>
+        </is>
+      </c>
+      <c r="S735" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="T735" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="U735" s="2" t="inlineStr"/>
+      <c r="V735" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@EnoeventosImportadora</t>
+        </is>
+      </c>
+      <c r="W735" s="2" t="inlineStr">
+        <is>
+          <t>Oscar Daudt</t>
+        </is>
+      </c>
+      <c r="X735" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y735" s="2" t="inlineStr"/>
+      <c r="Z735" s="2" t="inlineStr"/>
+      <c r="AA735" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/oscar-daudt-554623a2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="inlineStr">
+        <is>
+          <t>Hannover Comercio Importacao E Exportacao Ltda</t>
+        </is>
+      </c>
+      <c r="B736" s="2" t="inlineStr">
+        <is>
+          <t>Hannover Comercio Importacao E Exportacao Ltda</t>
+        </is>
+      </c>
+      <c r="C736" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="D736" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E736" s="2" t="inlineStr">
+        <is>
+          <t>Santa Maria Goretti</t>
+        </is>
+      </c>
+      <c r="F736" s="2" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G736" s="2" t="inlineStr">
+        <is>
+          <t>710 Rua Cerro Azul</t>
+        </is>
+      </c>
+      <c r="H736" s="2" t="inlineStr">
+        <is>
+          <t>91030-250</t>
+        </is>
+      </c>
+      <c r="I736" s="2" t="inlineStr">
+        <is>
+          <t>http://www.hannovervinhos.com.br</t>
+        </is>
+      </c>
+      <c r="J736" s="2" t="inlineStr"/>
+      <c r="K736" s="2" t="inlineStr"/>
+      <c r="L736" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M736" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N736" s="2" t="inlineStr">
+        <is>
+          <t>hannover@hannovervinhos.com.br</t>
+        </is>
+      </c>
+      <c r="O736" s="2" t="inlineStr">
+        <is>
+          <t>+55 51 3337-3890</t>
+        </is>
+      </c>
+      <c r="P736" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q736" s="2" t="inlineStr">
+        <is>
+          <t>91636944000105</t>
+        </is>
+      </c>
+      <c r="R736" s="2" t="inlineStr"/>
+      <c r="S736" s="2" t="inlineStr"/>
+      <c r="T736" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hannovervinhos/</t>
+        </is>
+      </c>
+      <c r="U736" s="2" t="inlineStr"/>
+      <c r="V736" s="2" t="inlineStr"/>
+      <c r="W736" s="2" t="inlineStr">
+        <is>
+          <t>Sergio Fernandes</t>
+        </is>
+      </c>
+      <c r="X736" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y736" s="2" t="inlineStr"/>
+      <c r="Z736" s="2" t="inlineStr"/>
+      <c r="AA736" s="2" t="inlineStr">
+        <is>
+          <t>https://br.linkedin.com/in/sergio-fernandes-36aa3b54/en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Brazil.xlsx
+++ b/BWI/bestwine_output/bestwine_Brazil.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA736"/>
+  <dimension ref="A1:AA771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -79852,6 +79852,3697 @@
         </is>
       </c>
     </row>
+    <row r="737">
+      <c r="A737" s="2" t="inlineStr">
+        <is>
+          <t>Wine To You</t>
+        </is>
+      </c>
+      <c r="B737" s="2" t="inlineStr">
+        <is>
+          <t>Wine To You</t>
+        </is>
+      </c>
+      <c r="C737" s="2" t="inlineStr">
+        <is>
+          <t>62603</t>
+        </is>
+      </c>
+      <c r="D737" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E737" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F737" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Consolacao</t>
+        </is>
+      </c>
+      <c r="G737" s="2" t="inlineStr">
+        <is>
+          <t>Rua Martinico Prado</t>
+        </is>
+      </c>
+      <c r="H737" s="2" t="inlineStr">
+        <is>
+          <t>01224-011</t>
+        </is>
+      </c>
+      <c r="I737" s="2" t="inlineStr">
+        <is>
+          <t>https://winetoyou.com.br</t>
+        </is>
+      </c>
+      <c r="J737" s="2" t="inlineStr"/>
+      <c r="K737" s="2" t="inlineStr"/>
+      <c r="L737" s="2" t="inlineStr"/>
+      <c r="M737" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N737" s="2" t="inlineStr">
+        <is>
+          <t>contato@winetoyou.com.br</t>
+        </is>
+      </c>
+      <c r="O737" s="2" t="inlineStr"/>
+      <c r="P737" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q737" s="2" t="inlineStr">
+        <is>
+          <t>24583265000128</t>
+        </is>
+      </c>
+      <c r="R737" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winetoyouoficial/</t>
+        </is>
+      </c>
+      <c r="S737" s="2" t="inlineStr"/>
+      <c r="T737" s="2" t="inlineStr"/>
+      <c r="U737" s="2" t="inlineStr"/>
+      <c r="V737" s="2" t="inlineStr"/>
+      <c r="W737" s="2" t="inlineStr"/>
+      <c r="X737" s="2" t="inlineStr"/>
+      <c r="Y737" s="2" t="inlineStr"/>
+      <c r="Z737" s="2" t="inlineStr"/>
+      <c r="AA737" s="2" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="inlineStr">
+        <is>
+          <t>Adega Bom Retiro</t>
+        </is>
+      </c>
+      <c r="B738" s="2" t="inlineStr">
+        <is>
+          <t>Adega Bom Retiro</t>
+        </is>
+      </c>
+      <c r="C738" s="2" t="inlineStr">
+        <is>
+          <t>59397</t>
+        </is>
+      </c>
+      <c r="D738" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E738" s="2" t="inlineStr">
+        <is>
+          <t>Bom Retiro</t>
+        </is>
+      </c>
+      <c r="F738" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G738" s="2" t="inlineStr">
+        <is>
+          <t>226 Rua Ribeiro de Lima</t>
+        </is>
+      </c>
+      <c r="H738" s="2" t="inlineStr">
+        <is>
+          <t>01122-000</t>
+        </is>
+      </c>
+      <c r="I738" s="2" t="inlineStr">
+        <is>
+          <t>https://adegabomretiro.com.br, https://adegabomretiro.loja2.com.br</t>
+        </is>
+      </c>
+      <c r="J738" s="2" t="inlineStr"/>
+      <c r="K738" s="2" t="inlineStr"/>
+      <c r="L738" s="2" t="inlineStr"/>
+      <c r="M738" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N738" s="2" t="inlineStr">
+        <is>
+          <t>adegabomretiro@uol.com.br</t>
+        </is>
+      </c>
+      <c r="O738" s="2" t="inlineStr">
+        <is>
+          <t>+55 11 3326-5214</t>
+        </is>
+      </c>
+      <c r="P738" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q738" s="2" t="inlineStr"/>
+      <c r="R738" s="2" t="inlineStr"/>
+      <c r="S738" s="2" t="inlineStr"/>
+      <c r="T738" s="2" t="inlineStr"/>
+      <c r="U738" s="2" t="inlineStr"/>
+      <c r="V738" s="2" t="inlineStr"/>
+      <c r="W738" s="2" t="inlineStr">
+        <is>
+          <t>Odair Machado</t>
+        </is>
+      </c>
+      <c r="X738" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y738" s="2" t="inlineStr"/>
+      <c r="Z738" s="2" t="inlineStr"/>
+      <c r="AA738" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/odair-machado-473182145/</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="2" t="inlineStr">
+        <is>
+          <t>Rota Do Azeite E Vinhos</t>
+        </is>
+      </c>
+      <c r="B739" s="2" t="inlineStr">
+        <is>
+          <t>Rota Do Azeite E Vinhos</t>
+        </is>
+      </c>
+      <c r="C739" s="2" t="inlineStr">
+        <is>
+          <t>121830</t>
+        </is>
+      </c>
+      <c r="D739" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E739" s="2" t="inlineStr">
+        <is>
+          <t>Vila Sao Francisco</t>
+        </is>
+      </c>
+      <c r="F739" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G739" s="2" t="inlineStr">
+        <is>
+          <t>522 Rua Noel José da Silva</t>
+        </is>
+      </c>
+      <c r="H739" s="2" t="inlineStr">
+        <is>
+          <t>03678-030</t>
+        </is>
+      </c>
+      <c r="I739" s="2" t="inlineStr">
+        <is>
+          <t>https://melhoresazeitesevinhos.com.br</t>
+        </is>
+      </c>
+      <c r="J739" s="2" t="inlineStr"/>
+      <c r="K739" s="2" t="inlineStr"/>
+      <c r="L739" s="2" t="inlineStr"/>
+      <c r="M739" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N739" s="2" t="inlineStr">
+        <is>
+          <t>rotadoazeitebr@hotmail.com</t>
+        </is>
+      </c>
+      <c r="O739" s="2" t="inlineStr">
+        <is>
+          <t>+55 11 2957-2768</t>
+        </is>
+      </c>
+      <c r="P739" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q739" s="2" t="inlineStr"/>
+      <c r="R739" s="2" t="inlineStr"/>
+      <c r="S739" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/rotadoazeitebr</t>
+        </is>
+      </c>
+      <c r="T739" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rotadoazeiteevinhos/</t>
+        </is>
+      </c>
+      <c r="U739" s="2" t="inlineStr"/>
+      <c r="V739" s="2" t="inlineStr"/>
+      <c r="W739" s="2" t="inlineStr">
+        <is>
+          <t>Elisabeth Mendes</t>
+        </is>
+      </c>
+      <c r="X739" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y739" s="2" t="inlineStr"/>
+      <c r="Z739" s="2" t="inlineStr"/>
+      <c r="AA739" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elisabeth-mendes-beth-mendes284-273a4938/</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="inlineStr">
+        <is>
+          <t>Vero Do Brasil Industria E Comercio Eireli</t>
+        </is>
+      </c>
+      <c r="B740" s="2" t="inlineStr">
+        <is>
+          <t>Vero Do Brasil Industria E Comercio Eireli</t>
+        </is>
+      </c>
+      <c r="C740" s="2" t="inlineStr">
+        <is>
+          <t>121831</t>
+        </is>
+      </c>
+      <c r="D740" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E740" s="2" t="inlineStr">
+        <is>
+          <t>Americanópolis</t>
+        </is>
+      </c>
+      <c r="F740" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G740" s="2" t="inlineStr">
+        <is>
+          <t>84 Rua Jacinto Paes</t>
+        </is>
+      </c>
+      <c r="H740" s="2" t="inlineStr">
+        <is>
+          <t>04338-090</t>
+        </is>
+      </c>
+      <c r="I740" s="2" t="inlineStr">
+        <is>
+          <t>https://www.verodobrasil.com.br</t>
+        </is>
+      </c>
+      <c r="J740" s="2" t="inlineStr"/>
+      <c r="K740" s="2" t="inlineStr"/>
+      <c r="L740" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M740" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N740" s="2" t="inlineStr">
+        <is>
+          <t>atendimento@verodobrasil.com.br</t>
+        </is>
+      </c>
+      <c r="O740" s="2" t="inlineStr">
+        <is>
+          <t>+55 11 5622-8000</t>
+        </is>
+      </c>
+      <c r="P740" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q740" s="2" t="inlineStr">
+        <is>
+          <t>04290436000113</t>
+        </is>
+      </c>
+      <c r="R740" s="2" t="inlineStr"/>
+      <c r="S740" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/verodobrasil/</t>
+        </is>
+      </c>
+      <c r="T740" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/verodobrasil/</t>
+        </is>
+      </c>
+      <c r="U740" s="2" t="inlineStr"/>
+      <c r="V740" s="2" t="inlineStr"/>
+      <c r="W740" s="2" t="inlineStr"/>
+      <c r="X740" s="2" t="inlineStr"/>
+      <c r="Y740" s="2" t="inlineStr"/>
+      <c r="Z740" s="2" t="inlineStr"/>
+      <c r="AA740" s="2" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="inlineStr">
+        <is>
+          <t>Rede Super</t>
+        </is>
+      </c>
+      <c r="B741" s="2" t="inlineStr">
+        <is>
+          <t>Rede Super</t>
+        </is>
+      </c>
+      <c r="C741" s="2" t="inlineStr">
+        <is>
+          <t>87072</t>
+        </is>
+      </c>
+      <c r="D741" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E741" s="2" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F741" s="2" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Santana do Livramento</t>
+        </is>
+      </c>
+      <c r="G741" s="2" t="inlineStr">
+        <is>
+          <t>20 Avenida Tamandaré</t>
+        </is>
+      </c>
+      <c r="H741" s="2" t="inlineStr">
+        <is>
+          <t>97573-520</t>
+        </is>
+      </c>
+      <c r="I741" s="2" t="inlineStr">
+        <is>
+          <t>https://lojas.redesuper.com, https://redesuper.com</t>
+        </is>
+      </c>
+      <c r="J741" s="2" t="inlineStr"/>
+      <c r="K741" s="2" t="inlineStr"/>
+      <c r="L741" s="2" t="inlineStr"/>
+      <c r="M741" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N741" s="2" t="inlineStr">
+        <is>
+          <t>pedidos2@redesuper.com</t>
+        </is>
+      </c>
+      <c r="O741" s="2" t="inlineStr">
+        <is>
+          <t>+55 800 51 7489</t>
+        </is>
+      </c>
+      <c r="P741" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q741" s="2" t="inlineStr"/>
+      <c r="R741" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/redesuperrs/</t>
+        </is>
+      </c>
+      <c r="S741" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/redesuperrs</t>
+        </is>
+      </c>
+      <c r="T741" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redesuperrs</t>
+        </is>
+      </c>
+      <c r="U741" s="2" t="inlineStr"/>
+      <c r="V741" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redesuper9895</t>
+        </is>
+      </c>
+      <c r="W741" s="2" t="inlineStr">
+        <is>
+          <t>Franciele Turra</t>
+        </is>
+      </c>
+      <c r="X741" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y741" s="2" t="inlineStr"/>
+      <c r="Z741" s="2" t="inlineStr"/>
+      <c r="AA741" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/franciele-turra-49592283/</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="inlineStr">
+        <is>
+          <t>Rede Super</t>
+        </is>
+      </c>
+      <c r="B742" s="2" t="inlineStr">
+        <is>
+          <t>Rede Super</t>
+        </is>
+      </c>
+      <c r="C742" s="2" t="inlineStr">
+        <is>
+          <t>87072</t>
+        </is>
+      </c>
+      <c r="D742" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E742" s="2" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F742" s="2" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Santana do Livramento</t>
+        </is>
+      </c>
+      <c r="G742" s="2" t="inlineStr">
+        <is>
+          <t>20 Avenida Tamandaré</t>
+        </is>
+      </c>
+      <c r="H742" s="2" t="inlineStr">
+        <is>
+          <t>97573-520</t>
+        </is>
+      </c>
+      <c r="I742" s="2" t="inlineStr">
+        <is>
+          <t>https://lojas.redesuper.com, https://redesuper.com</t>
+        </is>
+      </c>
+      <c r="J742" s="2" t="inlineStr"/>
+      <c r="K742" s="2" t="inlineStr"/>
+      <c r="L742" s="2" t="inlineStr"/>
+      <c r="M742" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N742" s="2" t="inlineStr">
+        <is>
+          <t>pedidos2@redesuper.com</t>
+        </is>
+      </c>
+      <c r="O742" s="2" t="inlineStr">
+        <is>
+          <t>+55 800 51 7489</t>
+        </is>
+      </c>
+      <c r="P742" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q742" s="2" t="inlineStr"/>
+      <c r="R742" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/redesuperrs/</t>
+        </is>
+      </c>
+      <c r="S742" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/redesuperrs</t>
+        </is>
+      </c>
+      <c r="T742" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redesuperrs</t>
+        </is>
+      </c>
+      <c r="U742" s="2" t="inlineStr"/>
+      <c r="V742" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redesuper9895</t>
+        </is>
+      </c>
+      <c r="W742" s="2" t="inlineStr">
+        <is>
+          <t>Renato Cemin</t>
+        </is>
+      </c>
+      <c r="X742" s="2" t="inlineStr">
+        <is>
+          <t>Store Manager</t>
+        </is>
+      </c>
+      <c r="Y742" s="2" t="inlineStr"/>
+      <c r="Z742" s="2" t="inlineStr"/>
+      <c r="AA742" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/renato-cemin-5639911b4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="inlineStr">
+        <is>
+          <t>Recofran Filial 1</t>
+        </is>
+      </c>
+      <c r="B743" s="2" t="inlineStr">
+        <is>
+          <t>Recofran Filial 1</t>
+        </is>
+      </c>
+      <c r="C743" s="2" t="inlineStr">
+        <is>
+          <t>86956</t>
+        </is>
+      </c>
+      <c r="D743" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E743" s="2" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F743" s="2" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Santana do Livramento</t>
+        </is>
+      </c>
+      <c r="G743" s="2" t="inlineStr">
+        <is>
+          <t>700 Avenida Francisco Reverbel de Araújo Góes</t>
+        </is>
+      </c>
+      <c r="H743" s="2" t="inlineStr">
+        <is>
+          <t>97574-760</t>
+        </is>
+      </c>
+      <c r="I743" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recofran.com</t>
+        </is>
+      </c>
+      <c r="J743" s="2" t="inlineStr"/>
+      <c r="K743" s="2" t="inlineStr"/>
+      <c r="L743" s="2" t="inlineStr"/>
+      <c r="M743" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N743" s="2" t="inlineStr">
+        <is>
+          <t>marketing@recofran.com.br</t>
+        </is>
+      </c>
+      <c r="O743" s="2" t="inlineStr">
+        <is>
+          <t>+55 55 3243-2121</t>
+        </is>
+      </c>
+      <c r="P743" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q743" s="2" t="inlineStr"/>
+      <c r="R743" s="2" t="inlineStr"/>
+      <c r="S743" s="2" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/recofran</t>
+        </is>
+      </c>
+      <c r="T743" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/recofrandelicia</t>
+        </is>
+      </c>
+      <c r="U743" s="2" t="inlineStr"/>
+      <c r="V743" s="2" t="inlineStr"/>
+      <c r="W743" s="2" t="inlineStr"/>
+      <c r="X743" s="2" t="inlineStr"/>
+      <c r="Y743" s="2" t="inlineStr"/>
+      <c r="Z743" s="2" t="inlineStr"/>
+      <c r="AA743" s="2" t="inlineStr"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B744" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C744" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="D744" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E744" s="2" t="inlineStr">
+        <is>
+          <t>Porto Belo</t>
+        </is>
+      </c>
+      <c r="F744" s="2" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="G744" s="2" t="inlineStr">
+        <is>
+          <t>Rod. Br 101, S/n Km 156,5 Sala 01</t>
+        </is>
+      </c>
+      <c r="H744" s="2" t="inlineStr">
+        <is>
+          <t>88210-000</t>
+        </is>
+      </c>
+      <c r="I744" s="2" t="inlineStr">
+        <is>
+          <t>https://super.angeloni.com.br, https://www.angeloni.com.br, https://www.divvino.com.br</t>
+        </is>
+      </c>
+      <c r="J744" s="2" t="inlineStr"/>
+      <c r="K744" s="2" t="inlineStr"/>
+      <c r="L744" s="2" t="inlineStr"/>
+      <c r="M744" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N744" s="2" t="inlineStr">
+        <is>
+          <t>atendimento@angeloni.com.br</t>
+        </is>
+      </c>
+      <c r="O744" s="2" t="inlineStr">
+        <is>
+          <t>+55 48 4042-0348</t>
+        </is>
+      </c>
+      <c r="P744" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q744" s="2" t="inlineStr"/>
+      <c r="R744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/angeloni/</t>
+        </is>
+      </c>
+      <c r="S744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RedeAngeloni/</t>
+        </is>
+      </c>
+      <c r="T744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redeangeloni/</t>
+        </is>
+      </c>
+      <c r="U744" s="2" t="inlineStr"/>
+      <c r="V744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redeangeloni/</t>
+        </is>
+      </c>
+      <c r="W744" s="2" t="inlineStr">
+        <is>
+          <t>Lucas Dahmer Mattos</t>
+        </is>
+      </c>
+      <c r="X744" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y744" s="2" t="inlineStr"/>
+      <c r="Z744" s="2" t="inlineStr"/>
+      <c r="AA744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lucas-dahmer-mattos-4b17988b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B745" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C745" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="D745" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E745" s="2" t="inlineStr">
+        <is>
+          <t>Porto Belo</t>
+        </is>
+      </c>
+      <c r="F745" s="2" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="G745" s="2" t="inlineStr">
+        <is>
+          <t>Rod. Br 101, S/n Km 156,5 Sala 01</t>
+        </is>
+      </c>
+      <c r="H745" s="2" t="inlineStr">
+        <is>
+          <t>88210-000</t>
+        </is>
+      </c>
+      <c r="I745" s="2" t="inlineStr">
+        <is>
+          <t>https://super.angeloni.com.br, https://www.angeloni.com.br, https://www.divvino.com.br</t>
+        </is>
+      </c>
+      <c r="J745" s="2" t="inlineStr"/>
+      <c r="K745" s="2" t="inlineStr"/>
+      <c r="L745" s="2" t="inlineStr"/>
+      <c r="M745" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N745" s="2" t="inlineStr">
+        <is>
+          <t>atendimento@angeloni.com.br</t>
+        </is>
+      </c>
+      <c r="O745" s="2" t="inlineStr">
+        <is>
+          <t>+55 48 4042-0348</t>
+        </is>
+      </c>
+      <c r="P745" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q745" s="2" t="inlineStr"/>
+      <c r="R745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/angeloni/</t>
+        </is>
+      </c>
+      <c r="S745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RedeAngeloni/</t>
+        </is>
+      </c>
+      <c r="T745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redeangeloni/</t>
+        </is>
+      </c>
+      <c r="U745" s="2" t="inlineStr"/>
+      <c r="V745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redeangeloni/</t>
+        </is>
+      </c>
+      <c r="W745" s="2" t="inlineStr">
+        <is>
+          <t>Rubia de Oliveira</t>
+        </is>
+      </c>
+      <c r="X745" s="2" t="inlineStr">
+        <is>
+          <t>International Business Manager</t>
+        </is>
+      </c>
+      <c r="Y745" s="2" t="inlineStr"/>
+      <c r="Z745" s="2" t="inlineStr"/>
+      <c r="AA745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rubiaoliveiras/</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B746" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C746" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="D746" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E746" s="2" t="inlineStr">
+        <is>
+          <t>Porto Belo</t>
+        </is>
+      </c>
+      <c r="F746" s="2" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="G746" s="2" t="inlineStr">
+        <is>
+          <t>Rod. Br 101, S/n Km 156,5 Sala 01</t>
+        </is>
+      </c>
+      <c r="H746" s="2" t="inlineStr">
+        <is>
+          <t>88210-000</t>
+        </is>
+      </c>
+      <c r="I746" s="2" t="inlineStr">
+        <is>
+          <t>https://super.angeloni.com.br, https://www.angeloni.com.br, https://www.divvino.com.br</t>
+        </is>
+      </c>
+      <c r="J746" s="2" t="inlineStr"/>
+      <c r="K746" s="2" t="inlineStr"/>
+      <c r="L746" s="2" t="inlineStr"/>
+      <c r="M746" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N746" s="2" t="inlineStr">
+        <is>
+          <t>atendimento@angeloni.com.br</t>
+        </is>
+      </c>
+      <c r="O746" s="2" t="inlineStr">
+        <is>
+          <t>+55 48 4042-0348</t>
+        </is>
+      </c>
+      <c r="P746" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q746" s="2" t="inlineStr"/>
+      <c r="R746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/angeloni/</t>
+        </is>
+      </c>
+      <c r="S746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RedeAngeloni/</t>
+        </is>
+      </c>
+      <c r="T746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redeangeloni/</t>
+        </is>
+      </c>
+      <c r="U746" s="2" t="inlineStr"/>
+      <c r="V746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redeangeloni/</t>
+        </is>
+      </c>
+      <c r="W746" s="2" t="inlineStr">
+        <is>
+          <t>Vanessa Schneider</t>
+        </is>
+      </c>
+      <c r="X746" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y746" s="2" t="inlineStr"/>
+      <c r="Z746" s="2" t="inlineStr"/>
+      <c r="AA746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vanessa-schneider-738846131/</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B747" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C747" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="D747" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E747" s="2" t="inlineStr">
+        <is>
+          <t>Porto Belo</t>
+        </is>
+      </c>
+      <c r="F747" s="2" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="G747" s="2" t="inlineStr">
+        <is>
+          <t>Rod. Br 101, S/n Km 156,5 Sala 01</t>
+        </is>
+      </c>
+      <c r="H747" s="2" t="inlineStr">
+        <is>
+          <t>88210-000</t>
+        </is>
+      </c>
+      <c r="I747" s="2" t="inlineStr">
+        <is>
+          <t>https://super.angeloni.com.br, https://www.angeloni.com.br, https://www.divvino.com.br</t>
+        </is>
+      </c>
+      <c r="J747" s="2" t="inlineStr"/>
+      <c r="K747" s="2" t="inlineStr"/>
+      <c r="L747" s="2" t="inlineStr"/>
+      <c r="M747" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N747" s="2" t="inlineStr">
+        <is>
+          <t>atendimento@angeloni.com.br</t>
+        </is>
+      </c>
+      <c r="O747" s="2" t="inlineStr">
+        <is>
+          <t>+55 48 4042-0348</t>
+        </is>
+      </c>
+      <c r="P747" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q747" s="2" t="inlineStr"/>
+      <c r="R747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/angeloni/</t>
+        </is>
+      </c>
+      <c r="S747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RedeAngeloni/</t>
+        </is>
+      </c>
+      <c r="T747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redeangeloni/</t>
+        </is>
+      </c>
+      <c r="U747" s="2" t="inlineStr"/>
+      <c r="V747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redeangeloni/</t>
+        </is>
+      </c>
+      <c r="W747" s="2" t="inlineStr">
+        <is>
+          <t>Mario Spillere</t>
+        </is>
+      </c>
+      <c r="X747" s="2" t="inlineStr">
+        <is>
+          <t>Wine Buyer</t>
+        </is>
+      </c>
+      <c r="Y747" s="2" t="inlineStr"/>
+      <c r="Z747" s="2" t="inlineStr"/>
+      <c r="AA747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mario-spillere-028511212/</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B748" s="2" t="inlineStr">
+        <is>
+          <t>A. Angeloni &amp; Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C748" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="D748" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E748" s="2" t="inlineStr">
+        <is>
+          <t>Porto Belo</t>
+        </is>
+      </c>
+      <c r="F748" s="2" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="G748" s="2" t="inlineStr">
+        <is>
+          <t>Rod. Br 101, S/n Km 156,5 Sala 01</t>
+        </is>
+      </c>
+      <c r="H748" s="2" t="inlineStr">
+        <is>
+          <t>88210-000</t>
+        </is>
+      </c>
+      <c r="I748" s="2" t="inlineStr">
+        <is>
+          <t>https://super.angeloni.com.br, https://www.angeloni.com.br, https://www.divvino.com.br</t>
+        </is>
+      </c>
+      <c r="J748" s="2" t="inlineStr"/>
+      <c r="K748" s="2" t="inlineStr"/>
+      <c r="L748" s="2" t="inlineStr"/>
+      <c r="M748" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N748" s="2" t="inlineStr">
+        <is>
+          <t>atendimento@angeloni.com.br</t>
+        </is>
+      </c>
+      <c r="O748" s="2" t="inlineStr">
+        <is>
+          <t>+55 48 4042-0348</t>
+        </is>
+      </c>
+      <c r="P748" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q748" s="2" t="inlineStr"/>
+      <c r="R748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/angeloni/</t>
+        </is>
+      </c>
+      <c r="S748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RedeAngeloni/</t>
+        </is>
+      </c>
+      <c r="T748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redeangeloni/</t>
+        </is>
+      </c>
+      <c r="U748" s="2" t="inlineStr"/>
+      <c r="V748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@redeangeloni/</t>
+        </is>
+      </c>
+      <c r="W748" s="2" t="inlineStr">
+        <is>
+          <t>Andre Meurer</t>
+        </is>
+      </c>
+      <c r="X748" s="2" t="inlineStr">
+        <is>
+          <t>Wine Consultant</t>
+        </is>
+      </c>
+      <c r="Y748" s="2" t="inlineStr"/>
+      <c r="Z748" s="2" t="inlineStr"/>
+      <c r="AA748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andre-meurer-4b94b41a1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="inlineStr">
+        <is>
+          <t>Jc Distribuicao Logistica Importacao E Exportacao De Produtos Industrializados Ltda</t>
+        </is>
+      </c>
+      <c r="B749" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JC Distribuição </t>
+        </is>
+      </c>
+      <c r="C749" s="2" t="inlineStr">
+        <is>
+          <t>121778</t>
+        </is>
+      </c>
+      <c r="D749" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E749" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Curitiba</t>
+        </is>
+      </c>
+      <c r="F749" s="2" t="inlineStr">
+        <is>
+          <t>Goiás, Goiânia</t>
+        </is>
+      </c>
+      <c r="G749" s="2" t="inlineStr">
+        <is>
+          <t>lt 02, 2 Avenida do Povo</t>
+        </is>
+      </c>
+      <c r="H749" s="2" t="inlineStr">
+        <is>
+          <t>74480-800</t>
+        </is>
+      </c>
+      <c r="I749" s="2" t="inlineStr">
+        <is>
+          <t>https://jcdistribuicao.com.br</t>
+        </is>
+      </c>
+      <c r="J749" s="2" t="inlineStr"/>
+      <c r="K749" s="2" t="inlineStr"/>
+      <c r="L749" s="2" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="M749" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N749" s="2" t="inlineStr">
+        <is>
+          <t>lorena.ramos@jcdistribuicao.com.br</t>
+        </is>
+      </c>
+      <c r="O749" s="2" t="inlineStr">
+        <is>
+          <t>+55 62 3240-9500</t>
+        </is>
+      </c>
+      <c r="P749" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q749" s="2" t="inlineStr">
+        <is>
+          <t>06314327000114</t>
+        </is>
+      </c>
+      <c r="R749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jc-distribui%C3%A7%C3%A3o/</t>
+        </is>
+      </c>
+      <c r="S749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/jcdistribuicaooficial</t>
+        </is>
+      </c>
+      <c r="T749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jcdistribuicao/</t>
+        </is>
+      </c>
+      <c r="U749" s="2" t="inlineStr"/>
+      <c r="V749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@tvjcdistribuicao3284/</t>
+        </is>
+      </c>
+      <c r="W749" s="2" t="inlineStr">
+        <is>
+          <t>Maxsuel Marques Ferreira Costa</t>
+        </is>
+      </c>
+      <c r="X749" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y749" s="2" t="inlineStr"/>
+      <c r="Z749" s="2" t="inlineStr"/>
+      <c r="AA749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maxsuel-marques-ferreira-costa-32a742196/</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="inlineStr">
+        <is>
+          <t>Jc Distribuicao Logistica Importacao E Exportacao De Produtos Industrializados Ltda</t>
+        </is>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JC Distribuição </t>
+        </is>
+      </c>
+      <c r="C750" s="2" t="inlineStr">
+        <is>
+          <t>121778</t>
+        </is>
+      </c>
+      <c r="D750" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E750" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Curitiba</t>
+        </is>
+      </c>
+      <c r="F750" s="2" t="inlineStr">
+        <is>
+          <t>Goiás, Goiânia</t>
+        </is>
+      </c>
+      <c r="G750" s="2" t="inlineStr">
+        <is>
+          <t>lt 02, 2 Avenida do Povo</t>
+        </is>
+      </c>
+      <c r="H750" s="2" t="inlineStr">
+        <is>
+          <t>74480-800</t>
+        </is>
+      </c>
+      <c r="I750" s="2" t="inlineStr">
+        <is>
+          <t>https://jcdistribuicao.com.br</t>
+        </is>
+      </c>
+      <c r="J750" s="2" t="inlineStr"/>
+      <c r="K750" s="2" t="inlineStr"/>
+      <c r="L750" s="2" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="M750" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N750" s="2" t="inlineStr">
+        <is>
+          <t>lorena.ramos@jcdistribuicao.com.br</t>
+        </is>
+      </c>
+      <c r="O750" s="2" t="inlineStr">
+        <is>
+          <t>+55 62 3240-9500</t>
+        </is>
+      </c>
+      <c r="P750" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q750" s="2" t="inlineStr">
+        <is>
+          <t>06314327000114</t>
+        </is>
+      </c>
+      <c r="R750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jc-distribui%C3%A7%C3%A3o/</t>
+        </is>
+      </c>
+      <c r="S750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/jcdistribuicaooficial</t>
+        </is>
+      </c>
+      <c r="T750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jcdistribuicao/</t>
+        </is>
+      </c>
+      <c r="U750" s="2" t="inlineStr"/>
+      <c r="V750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@tvjcdistribuicao3284/</t>
+        </is>
+      </c>
+      <c r="W750" s="2" t="inlineStr">
+        <is>
+          <t>Dielle Santis</t>
+        </is>
+      </c>
+      <c r="X750" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Assistant</t>
+        </is>
+      </c>
+      <c r="Y750" s="2" t="inlineStr"/>
+      <c r="Z750" s="2" t="inlineStr"/>
+      <c r="AA750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dielle-santis-4272aa203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="inlineStr">
+        <is>
+          <t>Jc Distribuicao Logistica Importacao E Exportacao De Produtos Industrializados Ltda</t>
+        </is>
+      </c>
+      <c r="B751" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JC Distribuição </t>
+        </is>
+      </c>
+      <c r="C751" s="2" t="inlineStr">
+        <is>
+          <t>121778</t>
+        </is>
+      </c>
+      <c r="D751" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E751" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Curitiba</t>
+        </is>
+      </c>
+      <c r="F751" s="2" t="inlineStr">
+        <is>
+          <t>Goiás, Goiânia</t>
+        </is>
+      </c>
+      <c r="G751" s="2" t="inlineStr">
+        <is>
+          <t>lt 02, 2 Avenida do Povo</t>
+        </is>
+      </c>
+      <c r="H751" s="2" t="inlineStr">
+        <is>
+          <t>74480-800</t>
+        </is>
+      </c>
+      <c r="I751" s="2" t="inlineStr">
+        <is>
+          <t>https://jcdistribuicao.com.br</t>
+        </is>
+      </c>
+      <c r="J751" s="2" t="inlineStr"/>
+      <c r="K751" s="2" t="inlineStr"/>
+      <c r="L751" s="2" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="M751" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N751" s="2" t="inlineStr">
+        <is>
+          <t>lorena.ramos@jcdistribuicao.com.br</t>
+        </is>
+      </c>
+      <c r="O751" s="2" t="inlineStr">
+        <is>
+          <t>+55 62 3240-9500</t>
+        </is>
+      </c>
+      <c r="P751" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q751" s="2" t="inlineStr">
+        <is>
+          <t>06314327000114</t>
+        </is>
+      </c>
+      <c r="R751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jc-distribui%C3%A7%C3%A3o/</t>
+        </is>
+      </c>
+      <c r="S751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/jcdistribuicaooficial</t>
+        </is>
+      </c>
+      <c r="T751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jcdistribuicao/</t>
+        </is>
+      </c>
+      <c r="U751" s="2" t="inlineStr"/>
+      <c r="V751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@tvjcdistribuicao3284/</t>
+        </is>
+      </c>
+      <c r="W751" s="2" t="inlineStr">
+        <is>
+          <t>Lorena Cerqueira</t>
+        </is>
+      </c>
+      <c r="X751" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Assistant</t>
+        </is>
+      </c>
+      <c r="Y751" s="2" t="inlineStr"/>
+      <c r="Z751" s="2" t="inlineStr"/>
+      <c r="AA751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lorena-cerqueira-ramos-62901b148/</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="inlineStr">
+        <is>
+          <t>Wine Out</t>
+        </is>
+      </c>
+      <c r="B752" s="2" t="inlineStr">
+        <is>
+          <t>Wine Out</t>
+        </is>
+      </c>
+      <c r="C752" s="2" t="inlineStr">
+        <is>
+          <t>97173</t>
+        </is>
+      </c>
+      <c r="D752" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E752" s="2" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F752" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Guarulhos</t>
+        </is>
+      </c>
+      <c r="G752" s="2" t="inlineStr">
+        <is>
+          <t>90 Rua Quinze de Novembro</t>
+        </is>
+      </c>
+      <c r="H752" s="2" t="inlineStr">
+        <is>
+          <t>07011-030</t>
+        </is>
+      </c>
+      <c r="I752" s="2" t="inlineStr">
+        <is>
+          <t>https://wineout.com.br</t>
+        </is>
+      </c>
+      <c r="J752" s="2" t="inlineStr"/>
+      <c r="K752" s="2" t="inlineStr"/>
+      <c r="L752" s="2" t="inlineStr"/>
+      <c r="M752" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N752" s="2" t="inlineStr">
+        <is>
+          <t>adm@wineout.com.br</t>
+        </is>
+      </c>
+      <c r="O752" s="2" t="inlineStr">
+        <is>
+          <t>+55 21 3827-0329</t>
+        </is>
+      </c>
+      <c r="P752" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q752" s="2" t="inlineStr"/>
+      <c r="R752" s="2" t="inlineStr"/>
+      <c r="S752" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineoutdistribuidora/</t>
+        </is>
+      </c>
+      <c r="T752" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineout_distribuidora/</t>
+        </is>
+      </c>
+      <c r="U752" s="2" t="inlineStr"/>
+      <c r="V752" s="2" t="inlineStr"/>
+      <c r="W752" s="2" t="inlineStr"/>
+      <c r="X752" s="2" t="inlineStr"/>
+      <c r="Y752" s="2" t="inlineStr"/>
+      <c r="Z752" s="2" t="inlineStr"/>
+      <c r="AA752" s="2" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="inlineStr">
+        <is>
+          <t>Megga Distribuidora Ltda</t>
+        </is>
+      </c>
+      <c r="B753" s="2" t="inlineStr"/>
+      <c r="C753" s="2" t="inlineStr">
+        <is>
+          <t>164233</t>
+        </is>
+      </c>
+      <c r="D753" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E753" s="2" t="inlineStr">
+        <is>
+          <t>Propriá</t>
+        </is>
+      </c>
+      <c r="F753" s="2" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="G753" s="2" t="inlineStr">
+        <is>
+          <t>1328 Rua Jessé Ferreira Trindade</t>
+        </is>
+      </c>
+      <c r="H753" s="2" t="inlineStr">
+        <is>
+          <t>49900-000</t>
+        </is>
+      </c>
+      <c r="I753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.meggadistribuidora.com.br</t>
+        </is>
+      </c>
+      <c r="J753" s="2" t="inlineStr"/>
+      <c r="K753" s="2" t="inlineStr"/>
+      <c r="L753" s="2" t="inlineStr"/>
+      <c r="M753" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N753" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce@meggadistribuidora.com.br</t>
+        </is>
+      </c>
+      <c r="O753" s="2" t="inlineStr"/>
+      <c r="P753" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q753" s="2" t="inlineStr"/>
+      <c r="R753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/grupomegga</t>
+        </is>
+      </c>
+      <c r="S753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/meggadistribuidorase/</t>
+        </is>
+      </c>
+      <c r="T753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/meggadistribuidorase/</t>
+        </is>
+      </c>
+      <c r="U753" s="2" t="inlineStr"/>
+      <c r="V753" s="2" t="inlineStr"/>
+      <c r="W753" s="2" t="inlineStr">
+        <is>
+          <t>Valdson Nunes</t>
+        </is>
+      </c>
+      <c r="X753" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y753" s="2" t="inlineStr"/>
+      <c r="Z753" s="2" t="inlineStr"/>
+      <c r="AA753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/valdson-nunes-327a12103/</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="inlineStr">
+        <is>
+          <t>Megga Distribuidora Ltda</t>
+        </is>
+      </c>
+      <c r="B754" s="2" t="inlineStr"/>
+      <c r="C754" s="2" t="inlineStr">
+        <is>
+          <t>164233</t>
+        </is>
+      </c>
+      <c r="D754" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E754" s="2" t="inlineStr">
+        <is>
+          <t>Propriá</t>
+        </is>
+      </c>
+      <c r="F754" s="2" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="G754" s="2" t="inlineStr">
+        <is>
+          <t>1328 Rua Jessé Ferreira Trindade</t>
+        </is>
+      </c>
+      <c r="H754" s="2" t="inlineStr">
+        <is>
+          <t>49900-000</t>
+        </is>
+      </c>
+      <c r="I754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.meggadistribuidora.com.br</t>
+        </is>
+      </c>
+      <c r="J754" s="2" t="inlineStr"/>
+      <c r="K754" s="2" t="inlineStr"/>
+      <c r="L754" s="2" t="inlineStr"/>
+      <c r="M754" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N754" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce@meggadistribuidora.com.br</t>
+        </is>
+      </c>
+      <c r="O754" s="2" t="inlineStr"/>
+      <c r="P754" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q754" s="2" t="inlineStr"/>
+      <c r="R754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/grupomegga</t>
+        </is>
+      </c>
+      <c r="S754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/meggadistribuidorase/</t>
+        </is>
+      </c>
+      <c r="T754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/meggadistribuidorase/</t>
+        </is>
+      </c>
+      <c r="U754" s="2" t="inlineStr"/>
+      <c r="V754" s="2" t="inlineStr"/>
+      <c r="W754" s="2" t="inlineStr">
+        <is>
+          <t>Claudio Martins</t>
+        </is>
+      </c>
+      <c r="X754" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y754" s="2" t="inlineStr"/>
+      <c r="Z754" s="2" t="inlineStr"/>
+      <c r="AA754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/claudio-martins-3a83aa161/</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="inlineStr">
+        <is>
+          <t>Nova Mega G Atacadista De Alimentos Sa</t>
+        </is>
+      </c>
+      <c r="B755" s="2" t="inlineStr"/>
+      <c r="C755" s="2" t="inlineStr">
+        <is>
+          <t>164232</t>
+        </is>
+      </c>
+      <c r="D755" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E755" s="2" t="inlineStr">
+        <is>
+          <t>Jardim São Luís</t>
+        </is>
+      </c>
+      <c r="F755" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G755" s="2" t="inlineStr">
+        <is>
+          <t>573 Avenida Maria Coelho Aguiar</t>
+        </is>
+      </c>
+      <c r="H755" s="2" t="inlineStr">
+        <is>
+          <t>05813-040</t>
+        </is>
+      </c>
+      <c r="I755" s="2" t="inlineStr">
+        <is>
+          <t>https://megag.com.br</t>
+        </is>
+      </c>
+      <c r="J755" s="2" t="inlineStr"/>
+      <c r="K755" s="2" t="inlineStr"/>
+      <c r="L755" s="2" t="inlineStr"/>
+      <c r="M755" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N755" s="2" t="inlineStr">
+        <is>
+          <t>raquel.rabelo@megag.com.br</t>
+        </is>
+      </c>
+      <c r="O755" s="2" t="inlineStr"/>
+      <c r="P755" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q755" s="2" t="inlineStr"/>
+      <c r="R755" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/megag-alimentos/</t>
+        </is>
+      </c>
+      <c r="S755" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/megag.atacadistadealimentos/</t>
+        </is>
+      </c>
+      <c r="T755" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megagalimentosoficial/</t>
+        </is>
+      </c>
+      <c r="U755" s="2" t="inlineStr"/>
+      <c r="V755" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@megagalimentosoficial/</t>
+        </is>
+      </c>
+      <c r="W755" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Rabelo</t>
+        </is>
+      </c>
+      <c r="X755" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Assistant</t>
+        </is>
+      </c>
+      <c r="Y755" s="2" t="inlineStr"/>
+      <c r="Z755" s="2" t="inlineStr"/>
+      <c r="AA755" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/raquel-rabelo-39666418a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="inlineStr">
+        <is>
+          <t>Nova Mega G Atacadista De Alimentos Sa</t>
+        </is>
+      </c>
+      <c r="B756" s="2" t="inlineStr"/>
+      <c r="C756" s="2" t="inlineStr">
+        <is>
+          <t>164232</t>
+        </is>
+      </c>
+      <c r="D756" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E756" s="2" t="inlineStr">
+        <is>
+          <t>Jardim São Luís</t>
+        </is>
+      </c>
+      <c r="F756" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G756" s="2" t="inlineStr">
+        <is>
+          <t>573 Avenida Maria Coelho Aguiar</t>
+        </is>
+      </c>
+      <c r="H756" s="2" t="inlineStr">
+        <is>
+          <t>05813-040</t>
+        </is>
+      </c>
+      <c r="I756" s="2" t="inlineStr">
+        <is>
+          <t>https://megag.com.br</t>
+        </is>
+      </c>
+      <c r="J756" s="2" t="inlineStr"/>
+      <c r="K756" s="2" t="inlineStr"/>
+      <c r="L756" s="2" t="inlineStr"/>
+      <c r="M756" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N756" s="2" t="inlineStr">
+        <is>
+          <t>raquel.rabelo@megag.com.br</t>
+        </is>
+      </c>
+      <c r="O756" s="2" t="inlineStr"/>
+      <c r="P756" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q756" s="2" t="inlineStr"/>
+      <c r="R756" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/megag-alimentos/</t>
+        </is>
+      </c>
+      <c r="S756" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/megag.atacadistadealimentos/</t>
+        </is>
+      </c>
+      <c r="T756" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megagalimentosoficial/</t>
+        </is>
+      </c>
+      <c r="U756" s="2" t="inlineStr"/>
+      <c r="V756" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@megagalimentosoficial/</t>
+        </is>
+      </c>
+      <c r="W756" s="2" t="inlineStr">
+        <is>
+          <t>Thalita Costa</t>
+        </is>
+      </c>
+      <c r="X756" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Assistant</t>
+        </is>
+      </c>
+      <c r="Y756" s="2" t="inlineStr"/>
+      <c r="Z756" s="2" t="inlineStr"/>
+      <c r="AA756" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thalita-costa-232b8517b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="inlineStr">
+        <is>
+          <t>Adega Franco Comercio De Bebidas Eireli</t>
+        </is>
+      </c>
+      <c r="B757" s="2" t="inlineStr">
+        <is>
+          <t>Adega Franco Comercio De Bebidas Eireli</t>
+        </is>
+      </c>
+      <c r="C757" s="2" t="inlineStr">
+        <is>
+          <t>59381</t>
+        </is>
+      </c>
+      <c r="D757" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E757" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Lange</t>
+        </is>
+      </c>
+      <c r="F757" s="2" t="inlineStr">
+        <is>
+          <t>Paraná, Curitiba</t>
+        </is>
+      </c>
+      <c r="G757" s="2" t="inlineStr">
+        <is>
+          <t>1320 Rua Augusto Stresser</t>
+        </is>
+      </c>
+      <c r="H757" s="2" t="inlineStr">
+        <is>
+          <t>80040-310</t>
+        </is>
+      </c>
+      <c r="I757" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adegafranco.com.br</t>
+        </is>
+      </c>
+      <c r="J757" s="2" t="inlineStr"/>
+      <c r="K757" s="2" t="inlineStr"/>
+      <c r="L757" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M757" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N757" s="2" t="inlineStr">
+        <is>
+          <t>guilherme@adegafranco.com.br</t>
+        </is>
+      </c>
+      <c r="O757" s="2" t="inlineStr">
+        <is>
+          <t>+55 41 3362-2265</t>
+        </is>
+      </c>
+      <c r="P757" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q757" s="2" t="inlineStr">
+        <is>
+          <t>10228713000160</t>
+        </is>
+      </c>
+      <c r="R757" s="2" t="inlineStr"/>
+      <c r="S757" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.facebook.com/aadegafrancolojadevinhos/?rf=143502249051512</t>
+        </is>
+      </c>
+      <c r="T757" s="2" t="inlineStr"/>
+      <c r="U757" s="2" t="inlineStr"/>
+      <c r="V757" s="2" t="inlineStr"/>
+      <c r="W757" s="2" t="inlineStr">
+        <is>
+          <t>Guilherme Franco</t>
+        </is>
+      </c>
+      <c r="X757" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y757" s="2" t="inlineStr"/>
+      <c r="Z757" s="2" t="inlineStr"/>
+      <c r="AA757" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/guilherme-franco-15024714/</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="inlineStr">
+        <is>
+          <t>Silva E Barbosa Comercio De Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="B758" s="2" t="inlineStr">
+        <is>
+          <t>Silva E Barbosa Comercio De Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="C758" s="2" t="inlineStr">
+        <is>
+          <t>157306</t>
+        </is>
+      </c>
+      <c r="D758" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E758" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Santa Rita</t>
+        </is>
+      </c>
+      <c r="F758" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Guarulhos</t>
+        </is>
+      </c>
+      <c r="G758" s="2" t="inlineStr">
+        <is>
+          <t>Rua Santo Antônio do Aventureiro</t>
+        </is>
+      </c>
+      <c r="H758" s="2" t="inlineStr">
+        <is>
+          <t>07143-040</t>
+        </is>
+      </c>
+      <c r="I758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.barbosasupermercados.com.br</t>
+        </is>
+      </c>
+      <c r="J758" s="2" t="inlineStr"/>
+      <c r="K758" s="2" t="inlineStr"/>
+      <c r="L758" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="M758" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N758" s="2" t="inlineStr">
+        <is>
+          <t>pamela@barbosasm.com.br</t>
+        </is>
+      </c>
+      <c r="O758" s="2" t="inlineStr">
+        <is>
+          <t>+55 11 3003-2557</t>
+        </is>
+      </c>
+      <c r="P758" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q758" s="2" t="inlineStr">
+        <is>
+          <t>60437647000107</t>
+        </is>
+      </c>
+      <c r="R758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/barbosa-supermercados/</t>
+        </is>
+      </c>
+      <c r="S758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/barbosasm/</t>
+        </is>
+      </c>
+      <c r="T758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barbosasupermercados/</t>
+        </is>
+      </c>
+      <c r="U758" s="2" t="inlineStr"/>
+      <c r="V758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@barbosasupermercados6703/</t>
+        </is>
+      </c>
+      <c r="W758" s="2" t="inlineStr">
+        <is>
+          <t>Aluizio Luiz</t>
+        </is>
+      </c>
+      <c r="X758" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y758" s="2" t="inlineStr"/>
+      <c r="Z758" s="2" t="inlineStr"/>
+      <c r="AA758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aluizio-luiz-de-almeida-8b3779177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="inlineStr">
+        <is>
+          <t>Silva E Barbosa Comercio De Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="B759" s="2" t="inlineStr">
+        <is>
+          <t>Silva E Barbosa Comercio De Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="C759" s="2" t="inlineStr">
+        <is>
+          <t>157306</t>
+        </is>
+      </c>
+      <c r="D759" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E759" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Santa Rita</t>
+        </is>
+      </c>
+      <c r="F759" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Guarulhos</t>
+        </is>
+      </c>
+      <c r="G759" s="2" t="inlineStr">
+        <is>
+          <t>Rua Santo Antônio do Aventureiro</t>
+        </is>
+      </c>
+      <c r="H759" s="2" t="inlineStr">
+        <is>
+          <t>07143-040</t>
+        </is>
+      </c>
+      <c r="I759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.barbosasupermercados.com.br</t>
+        </is>
+      </c>
+      <c r="J759" s="2" t="inlineStr"/>
+      <c r="K759" s="2" t="inlineStr"/>
+      <c r="L759" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="M759" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N759" s="2" t="inlineStr">
+        <is>
+          <t>pamela@barbosasm.com.br</t>
+        </is>
+      </c>
+      <c r="O759" s="2" t="inlineStr">
+        <is>
+          <t>+55 11 3003-2557</t>
+        </is>
+      </c>
+      <c r="P759" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q759" s="2" t="inlineStr">
+        <is>
+          <t>60437647000107</t>
+        </is>
+      </c>
+      <c r="R759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/barbosa-supermercados/</t>
+        </is>
+      </c>
+      <c r="S759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/barbosasm/</t>
+        </is>
+      </c>
+      <c r="T759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barbosasupermercados/</t>
+        </is>
+      </c>
+      <c r="U759" s="2" t="inlineStr"/>
+      <c r="V759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@barbosasupermercados6703/</t>
+        </is>
+      </c>
+      <c r="W759" s="2" t="inlineStr">
+        <is>
+          <t>Augusto Navajas</t>
+        </is>
+      </c>
+      <c r="X759" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y759" s="2" t="inlineStr"/>
+      <c r="Z759" s="2" t="inlineStr"/>
+      <c r="AA759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/augusto-navajas-878134b6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="inlineStr">
+        <is>
+          <t>Silva E Barbosa Comercio De Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="B760" s="2" t="inlineStr">
+        <is>
+          <t>Silva E Barbosa Comercio De Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="C760" s="2" t="inlineStr">
+        <is>
+          <t>157306</t>
+        </is>
+      </c>
+      <c r="D760" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E760" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Santa Rita</t>
+        </is>
+      </c>
+      <c r="F760" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Guarulhos</t>
+        </is>
+      </c>
+      <c r="G760" s="2" t="inlineStr">
+        <is>
+          <t>Rua Santo Antônio do Aventureiro</t>
+        </is>
+      </c>
+      <c r="H760" s="2" t="inlineStr">
+        <is>
+          <t>07143-040</t>
+        </is>
+      </c>
+      <c r="I760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.barbosasupermercados.com.br</t>
+        </is>
+      </c>
+      <c r="J760" s="2" t="inlineStr"/>
+      <c r="K760" s="2" t="inlineStr"/>
+      <c r="L760" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="M760" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N760" s="2" t="inlineStr">
+        <is>
+          <t>pamela@barbosasm.com.br</t>
+        </is>
+      </c>
+      <c r="O760" s="2" t="inlineStr">
+        <is>
+          <t>+55 11 3003-2557</t>
+        </is>
+      </c>
+      <c r="P760" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q760" s="2" t="inlineStr">
+        <is>
+          <t>60437647000107</t>
+        </is>
+      </c>
+      <c r="R760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/barbosa-supermercados/</t>
+        </is>
+      </c>
+      <c r="S760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/barbosasm/</t>
+        </is>
+      </c>
+      <c r="T760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barbosasupermercados/</t>
+        </is>
+      </c>
+      <c r="U760" s="2" t="inlineStr"/>
+      <c r="V760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@barbosasupermercados6703/</t>
+        </is>
+      </c>
+      <c r="W760" s="2" t="inlineStr">
+        <is>
+          <t>Pamela Cristina</t>
+        </is>
+      </c>
+      <c r="X760" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y760" s="2" t="inlineStr"/>
+      <c r="Z760" s="2" t="inlineStr"/>
+      <c r="AA760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pamela-cristina-229463223/</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="inlineStr">
+        <is>
+          <t>Brindisi Vinhos Comércio De Bebidas Ltda.</t>
+        </is>
+      </c>
+      <c r="B761" s="2" t="inlineStr">
+        <is>
+          <t>Brindisi Vinhos Comércio De Bebidas Ltda.</t>
+        </is>
+      </c>
+      <c r="C761" s="2" t="inlineStr">
+        <is>
+          <t>50932</t>
+        </is>
+      </c>
+      <c r="D761" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E761" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Paulistano</t>
+        </is>
+      </c>
+      <c r="F761" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G761" s="2" t="inlineStr">
+        <is>
+          <t>187 Loja2 Rua Professor Artur Ramos</t>
+        </is>
+      </c>
+      <c r="H761" s="2" t="inlineStr">
+        <is>
+          <t>01454-011</t>
+        </is>
+      </c>
+      <c r="I761" s="2" t="inlineStr">
+        <is>
+          <t>https://brindisivinhos.com.br</t>
+        </is>
+      </c>
+      <c r="J761" s="2" t="inlineStr"/>
+      <c r="K761" s="2" t="inlineStr"/>
+      <c r="L761" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M761" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N761" s="2" t="inlineStr">
+        <is>
+          <t>sac@brindisivinhos.com.br</t>
+        </is>
+      </c>
+      <c r="O761" s="2" t="inlineStr"/>
+      <c r="P761" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q761" s="2" t="inlineStr">
+        <is>
+          <t>31139452000182</t>
+        </is>
+      </c>
+      <c r="R761" s="2" t="inlineStr"/>
+      <c r="S761" s="2" t="inlineStr"/>
+      <c r="T761" s="2" t="inlineStr"/>
+      <c r="U761" s="2" t="inlineStr"/>
+      <c r="V761" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/BrindisiVinhos</t>
+        </is>
+      </c>
+      <c r="W761" s="2" t="inlineStr">
+        <is>
+          <t>Luiz fernando</t>
+        </is>
+      </c>
+      <c r="X761" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y761" s="2" t="inlineStr"/>
+      <c r="Z761" s="2" t="inlineStr"/>
+      <c r="AA761" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luiz-fernando-de-almeida-lima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="inlineStr">
+        <is>
+          <t>Brindisi Vinhos Comércio De Bebidas Ltda.</t>
+        </is>
+      </c>
+      <c r="B762" s="2" t="inlineStr">
+        <is>
+          <t>Brindisi Vinhos Comércio De Bebidas Ltda.</t>
+        </is>
+      </c>
+      <c r="C762" s="2" t="inlineStr">
+        <is>
+          <t>50932</t>
+        </is>
+      </c>
+      <c r="D762" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E762" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Paulistano</t>
+        </is>
+      </c>
+      <c r="F762" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G762" s="2" t="inlineStr">
+        <is>
+          <t>187 Loja2 Rua Professor Artur Ramos</t>
+        </is>
+      </c>
+      <c r="H762" s="2" t="inlineStr">
+        <is>
+          <t>01454-011</t>
+        </is>
+      </c>
+      <c r="I762" s="2" t="inlineStr">
+        <is>
+          <t>https://brindisivinhos.com.br</t>
+        </is>
+      </c>
+      <c r="J762" s="2" t="inlineStr"/>
+      <c r="K762" s="2" t="inlineStr"/>
+      <c r="L762" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M762" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N762" s="2" t="inlineStr">
+        <is>
+          <t>sac@brindisivinhos.com.br</t>
+        </is>
+      </c>
+      <c r="O762" s="2" t="inlineStr"/>
+      <c r="P762" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q762" s="2" t="inlineStr">
+        <is>
+          <t>31139452000182</t>
+        </is>
+      </c>
+      <c r="R762" s="2" t="inlineStr"/>
+      <c r="S762" s="2" t="inlineStr"/>
+      <c r="T762" s="2" t="inlineStr"/>
+      <c r="U762" s="2" t="inlineStr"/>
+      <c r="V762" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/BrindisiVinhos</t>
+        </is>
+      </c>
+      <c r="W762" s="2" t="inlineStr">
+        <is>
+          <t>Ana Carla</t>
+        </is>
+      </c>
+      <c r="X762" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y762" s="2" t="inlineStr"/>
+      <c r="Z762" s="2" t="inlineStr"/>
+      <c r="AA762" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ana-carla-moraes-de-oliveira-74a03229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="inlineStr">
+        <is>
+          <t>L.s.a. Correa - Vinhos</t>
+        </is>
+      </c>
+      <c r="B763" s="2" t="inlineStr">
+        <is>
+          <t>L.s.a. Correa - Vinhos</t>
+        </is>
+      </c>
+      <c r="C763" s="2" t="inlineStr">
+        <is>
+          <t>111910</t>
+        </is>
+      </c>
+      <c r="D763" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E763" s="2" t="inlineStr">
+        <is>
+          <t>Gonzaga</t>
+        </is>
+      </c>
+      <c r="F763" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Santos</t>
+        </is>
+      </c>
+      <c r="G763" s="2" t="inlineStr">
+        <is>
+          <t>59 Avenida Ana Costa</t>
+        </is>
+      </c>
+      <c r="H763" s="2" t="inlineStr">
+        <is>
+          <t>11060-001</t>
+        </is>
+      </c>
+      <c r="I763" s="2" t="inlineStr">
+        <is>
+          <t>https://wine2go.com.br</t>
+        </is>
+      </c>
+      <c r="J763" s="2" t="inlineStr"/>
+      <c r="K763" s="2" t="inlineStr"/>
+      <c r="L763" s="2" t="inlineStr"/>
+      <c r="M763" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N763" s="2" t="inlineStr">
+        <is>
+          <t>fernanda@wine2go.com.br</t>
+        </is>
+      </c>
+      <c r="O763" s="2" t="inlineStr"/>
+      <c r="P763" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q763" s="2" t="inlineStr"/>
+      <c r="R763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine2go-brasil/</t>
+        </is>
+      </c>
+      <c r="S763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wine2gobrasil/</t>
+        </is>
+      </c>
+      <c r="T763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine2gobrasil</t>
+        </is>
+      </c>
+      <c r="U763" s="2" t="inlineStr"/>
+      <c r="V763" s="2" t="inlineStr"/>
+      <c r="W763" s="2" t="inlineStr">
+        <is>
+          <t>Fernanda Barreiros</t>
+        </is>
+      </c>
+      <c r="X763" s="2" t="inlineStr">
+        <is>
+          <t>Business Partner</t>
+        </is>
+      </c>
+      <c r="Y763" s="2" t="inlineStr"/>
+      <c r="Z763" s="2" t="inlineStr"/>
+      <c r="AA763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernanda-barreiros-2b8402270/</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="inlineStr">
+        <is>
+          <t>Cmp - Comércio, Importação E Exportação De Bebidas E Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="B764" s="2" t="inlineStr">
+        <is>
+          <t>Cmp - Comércio, Importação E Exportação De Bebidas E Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="C764" s="2" t="inlineStr">
+        <is>
+          <t>40916</t>
+        </is>
+      </c>
+      <c r="D764" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E764" s="2" t="inlineStr">
+        <is>
+          <t>Itaim Bibi</t>
+        </is>
+      </c>
+      <c r="F764" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G764" s="2" t="inlineStr">
+        <is>
+          <t>162 Rua Romilda Margarida Gabriel</t>
+        </is>
+      </c>
+      <c r="H764" s="2" t="inlineStr">
+        <is>
+          <t>04530-090</t>
+        </is>
+      </c>
+      <c r="I764" s="2" t="inlineStr">
+        <is>
+          <t>https://caveleman.com</t>
+        </is>
+      </c>
+      <c r="J764" s="2" t="inlineStr"/>
+      <c r="K764" s="2" t="inlineStr"/>
+      <c r="L764" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M764" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N764" s="2" t="inlineStr">
+        <is>
+          <t>marcio.morelli@caveleman.com.br</t>
+        </is>
+      </c>
+      <c r="O764" s="2" t="inlineStr"/>
+      <c r="P764" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q764" s="2" t="inlineStr">
+        <is>
+          <t>29686483000101</t>
+        </is>
+      </c>
+      <c r="R764" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cave-leman/</t>
+        </is>
+      </c>
+      <c r="S764" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.facebook.com/caveleman/</t>
+        </is>
+      </c>
+      <c r="T764" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/caveleman</t>
+        </is>
+      </c>
+      <c r="U764" s="2" t="inlineStr"/>
+      <c r="V764" s="2" t="inlineStr"/>
+      <c r="W764" s="2" t="inlineStr">
+        <is>
+          <t>Marcio Morelli</t>
+        </is>
+      </c>
+      <c r="X764" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y764" s="2" t="inlineStr"/>
+      <c r="Z764" s="2" t="inlineStr"/>
+      <c r="AA764" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marciomorelli/</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="inlineStr">
+        <is>
+          <t>Cmp - Comércio, Importação E Exportação De Bebidas E Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="B765" s="2" t="inlineStr">
+        <is>
+          <t>Cmp - Comércio, Importação E Exportação De Bebidas E Alimentos Ltda</t>
+        </is>
+      </c>
+      <c r="C765" s="2" t="inlineStr">
+        <is>
+          <t>40916</t>
+        </is>
+      </c>
+      <c r="D765" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E765" s="2" t="inlineStr">
+        <is>
+          <t>Itaim Bibi</t>
+        </is>
+      </c>
+      <c r="F765" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G765" s="2" t="inlineStr">
+        <is>
+          <t>162 Rua Romilda Margarida Gabriel</t>
+        </is>
+      </c>
+      <c r="H765" s="2" t="inlineStr">
+        <is>
+          <t>04530-090</t>
+        </is>
+      </c>
+      <c r="I765" s="2" t="inlineStr">
+        <is>
+          <t>https://caveleman.com</t>
+        </is>
+      </c>
+      <c r="J765" s="2" t="inlineStr"/>
+      <c r="K765" s="2" t="inlineStr"/>
+      <c r="L765" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M765" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N765" s="2" t="inlineStr">
+        <is>
+          <t>marcio.morelli@caveleman.com.br</t>
+        </is>
+      </c>
+      <c r="O765" s="2" t="inlineStr"/>
+      <c r="P765" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q765" s="2" t="inlineStr">
+        <is>
+          <t>29686483000101</t>
+        </is>
+      </c>
+      <c r="R765" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cave-leman/</t>
+        </is>
+      </c>
+      <c r="S765" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.facebook.com/caveleman/</t>
+        </is>
+      </c>
+      <c r="T765" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/caveleman</t>
+        </is>
+      </c>
+      <c r="U765" s="2" t="inlineStr"/>
+      <c r="V765" s="2" t="inlineStr"/>
+      <c r="W765" s="2" t="inlineStr">
+        <is>
+          <t>Lucas Toledo</t>
+        </is>
+      </c>
+      <c r="X765" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Representative</t>
+        </is>
+      </c>
+      <c r="Y765" s="2" t="inlineStr"/>
+      <c r="Z765" s="2" t="inlineStr"/>
+      <c r="AA765" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lucas-toledo-piza-amighini-8ab139137/</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="inlineStr">
+        <is>
+          <t>Comercial De Queijos E Vinhos Batel Eireli</t>
+        </is>
+      </c>
+      <c r="B766" s="2" t="inlineStr">
+        <is>
+          <t>Comercial De Queijos E Vinhos Batel Eireli</t>
+        </is>
+      </c>
+      <c r="C766" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D766" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E766" s="2" t="inlineStr">
+        <is>
+          <t>Batel</t>
+        </is>
+      </c>
+      <c r="F766" s="2" t="inlineStr">
+        <is>
+          <t>Paraná, Curitiba</t>
+        </is>
+      </c>
+      <c r="G766" s="2" t="inlineStr">
+        <is>
+          <t>1865 Avenida Sete de Setembro</t>
+        </is>
+      </c>
+      <c r="H766" s="2" t="inlineStr">
+        <is>
+          <t>80060-070</t>
+        </is>
+      </c>
+      <c r="I766" s="2" t="inlineStr">
+        <is>
+          <t>https://adegacuritibana.com.br</t>
+        </is>
+      </c>
+      <c r="J766" s="2" t="inlineStr"/>
+      <c r="K766" s="2" t="inlineStr"/>
+      <c r="L766" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M766" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N766" s="2" t="inlineStr">
+        <is>
+          <t>sac@adegacuritibana.com.br</t>
+        </is>
+      </c>
+      <c r="O766" s="2" t="inlineStr"/>
+      <c r="P766" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q766" s="2" t="inlineStr">
+        <is>
+          <t>09025700000105</t>
+        </is>
+      </c>
+      <c r="R766" s="2" t="inlineStr"/>
+      <c r="S766" s="2" t="inlineStr"/>
+      <c r="T766" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/adegacuritibana/</t>
+        </is>
+      </c>
+      <c r="U766" s="2" t="inlineStr"/>
+      <c r="V766" s="2" t="inlineStr"/>
+      <c r="W766" s="2" t="inlineStr">
+        <is>
+          <t>Maricel Heiden</t>
+        </is>
+      </c>
+      <c r="X766" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y766" s="2" t="inlineStr"/>
+      <c r="Z766" s="2" t="inlineStr"/>
+      <c r="AA766" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maricel-heiden-235a6a5b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda</t>
+        </is>
+      </c>
+      <c r="B767" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda.</t>
+        </is>
+      </c>
+      <c r="C767" s="2" t="inlineStr">
+        <is>
+          <t>121210</t>
+        </is>
+      </c>
+      <c r="D767" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E767" s="2" t="inlineStr">
+        <is>
+          <t>Moema</t>
+        </is>
+      </c>
+      <c r="F767" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G767" s="2" t="inlineStr">
+        <is>
+          <t>60 Avenida Rouxinol</t>
+        </is>
+      </c>
+      <c r="H767" s="2" t="inlineStr">
+        <is>
+          <t>04516-000</t>
+        </is>
+      </c>
+      <c r="I767" s="2" t="inlineStr">
+        <is>
+          <t>https://www.importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="J767" s="2" t="inlineStr"/>
+      <c r="K767" s="2" t="inlineStr"/>
+      <c r="L767" s="2" t="inlineStr"/>
+      <c r="M767" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N767" s="2" t="inlineStr">
+        <is>
+          <t>patricia.martins@importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="O767" s="2" t="inlineStr">
+        <is>
+          <t>+55 47 3048-0609</t>
+        </is>
+      </c>
+      <c r="P767" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q767" s="2" t="inlineStr">
+        <is>
+          <t>24004841000135</t>
+        </is>
+      </c>
+      <c r="R767" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boena-importadora/</t>
+        </is>
+      </c>
+      <c r="S767" s="2" t="inlineStr"/>
+      <c r="T767" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boenaimportadora/</t>
+        </is>
+      </c>
+      <c r="U767" s="2" t="inlineStr"/>
+      <c r="V767" s="2" t="inlineStr"/>
+      <c r="W767" s="2" t="inlineStr">
+        <is>
+          <t>Patricia F</t>
+        </is>
+      </c>
+      <c r="X767" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Manager</t>
+        </is>
+      </c>
+      <c r="Y767" s="2" t="inlineStr"/>
+      <c r="Z767" s="2" t="inlineStr"/>
+      <c r="AA767" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricia-f-martins-643a4320b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda</t>
+        </is>
+      </c>
+      <c r="B768" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Boena Ltda.</t>
+        </is>
+      </c>
+      <c r="C768" s="2" t="inlineStr">
+        <is>
+          <t>121210</t>
+        </is>
+      </c>
+      <c r="D768" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E768" s="2" t="inlineStr">
+        <is>
+          <t>Moema</t>
+        </is>
+      </c>
+      <c r="F768" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="G768" s="2" t="inlineStr">
+        <is>
+          <t>60 Avenida Rouxinol</t>
+        </is>
+      </c>
+      <c r="H768" s="2" t="inlineStr">
+        <is>
+          <t>04516-000</t>
+        </is>
+      </c>
+      <c r="I768" s="2" t="inlineStr">
+        <is>
+          <t>https://www.importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="J768" s="2" t="inlineStr"/>
+      <c r="K768" s="2" t="inlineStr"/>
+      <c r="L768" s="2" t="inlineStr"/>
+      <c r="M768" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N768" s="2" t="inlineStr">
+        <is>
+          <t>patricia.martins@importadoraboena.com.br</t>
+        </is>
+      </c>
+      <c r="O768" s="2" t="inlineStr">
+        <is>
+          <t>+55 47 3048-0609</t>
+        </is>
+      </c>
+      <c r="P768" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q768" s="2" t="inlineStr">
+        <is>
+          <t>24004841000135</t>
+        </is>
+      </c>
+      <c r="R768" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boena-importadora/</t>
+        </is>
+      </c>
+      <c r="S768" s="2" t="inlineStr"/>
+      <c r="T768" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boenaimportadora/</t>
+        </is>
+      </c>
+      <c r="U768" s="2" t="inlineStr"/>
+      <c r="V768" s="2" t="inlineStr"/>
+      <c r="W768" s="2" t="inlineStr">
+        <is>
+          <t>Newton Carlos</t>
+        </is>
+      </c>
+      <c r="X768" s="2" t="inlineStr">
+        <is>
+          <t>National Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y768" s="2" t="inlineStr"/>
+      <c r="Z768" s="2" t="inlineStr"/>
+      <c r="AA768" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/newton-carlos-almeida-9b40a458/</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="B769" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="C769" s="2" t="inlineStr">
+        <is>
+          <t>25723</t>
+        </is>
+      </c>
+      <c r="D769" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E769" s="2" t="inlineStr">
+        <is>
+          <t>Imperial de São Cristóvão</t>
+        </is>
+      </c>
+      <c r="F769" s="2" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G769" s="2" t="inlineStr">
+        <is>
+          <t>316 Avenida Pedro II</t>
+        </is>
+      </c>
+      <c r="H769" s="2" t="inlineStr">
+        <is>
+          <t>20941-070</t>
+        </is>
+      </c>
+      <c r="I769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lojaenoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="J769" s="2" t="inlineStr"/>
+      <c r="K769" s="2" t="inlineStr"/>
+      <c r="L769" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M769" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N769" s="2" t="inlineStr">
+        <is>
+          <t>tsalame@enoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="O769" s="2" t="inlineStr">
+        <is>
+          <t>+55 21 2042-8980</t>
+        </is>
+      </c>
+      <c r="P769" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q769" s="2" t="inlineStr">
+        <is>
+          <t>20345380000103</t>
+        </is>
+      </c>
+      <c r="R769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enoeventos-importadora-de-bebidas-ltda-/</t>
+        </is>
+      </c>
+      <c r="S769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="T769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="U769" s="2" t="inlineStr"/>
+      <c r="V769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@EnoeventosImportadora</t>
+        </is>
+      </c>
+      <c r="W769" s="2" t="inlineStr">
+        <is>
+          <t>Thiago Salame</t>
+        </is>
+      </c>
+      <c r="X769" s="2" t="inlineStr">
+        <is>
+          <t>Partner - Director</t>
+        </is>
+      </c>
+      <c r="Y769" s="2" t="inlineStr"/>
+      <c r="Z769" s="2" t="inlineStr"/>
+      <c r="AA769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thiago-salame-b2511024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="B770" s="2" t="inlineStr">
+        <is>
+          <t>Enoeventos Importadora De Bebidas Ltda</t>
+        </is>
+      </c>
+      <c r="C770" s="2" t="inlineStr">
+        <is>
+          <t>25723</t>
+        </is>
+      </c>
+      <c r="D770" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E770" s="2" t="inlineStr">
+        <is>
+          <t>Imperial de São Cristóvão</t>
+        </is>
+      </c>
+      <c r="F770" s="2" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G770" s="2" t="inlineStr">
+        <is>
+          <t>316 Avenida Pedro II</t>
+        </is>
+      </c>
+      <c r="H770" s="2" t="inlineStr">
+        <is>
+          <t>20941-070</t>
+        </is>
+      </c>
+      <c r="I770" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lojaenoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="J770" s="2" t="inlineStr"/>
+      <c r="K770" s="2" t="inlineStr"/>
+      <c r="L770" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M770" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N770" s="2" t="inlineStr">
+        <is>
+          <t>tsalame@enoeventos.com.br</t>
+        </is>
+      </c>
+      <c r="O770" s="2" t="inlineStr">
+        <is>
+          <t>+55 21 2042-8980</t>
+        </is>
+      </c>
+      <c r="P770" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q770" s="2" t="inlineStr">
+        <is>
+          <t>20345380000103</t>
+        </is>
+      </c>
+      <c r="R770" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enoeventos-importadora-de-bebidas-ltda-/</t>
+        </is>
+      </c>
+      <c r="S770" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="T770" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enoeventos</t>
+        </is>
+      </c>
+      <c r="U770" s="2" t="inlineStr"/>
+      <c r="V770" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@EnoeventosImportadora</t>
+        </is>
+      </c>
+      <c r="W770" s="2" t="inlineStr">
+        <is>
+          <t>Oscar Daudt</t>
+        </is>
+      </c>
+      <c r="X770" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y770" s="2" t="inlineStr"/>
+      <c r="Z770" s="2" t="inlineStr"/>
+      <c r="AA770" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/oscar-daudt-554623a2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="inlineStr">
+        <is>
+          <t>Hannover Comercio Importacao E Exportacao Ltda</t>
+        </is>
+      </c>
+      <c r="B771" s="2" t="inlineStr">
+        <is>
+          <t>Hannover Comercio Importacao E Exportacao Ltda</t>
+        </is>
+      </c>
+      <c r="C771" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="D771" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E771" s="2" t="inlineStr">
+        <is>
+          <t>Santa Maria Goretti</t>
+        </is>
+      </c>
+      <c r="F771" s="2" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G771" s="2" t="inlineStr">
+        <is>
+          <t>710 Rua Cerro Azul</t>
+        </is>
+      </c>
+      <c r="H771" s="2" t="inlineStr">
+        <is>
+          <t>91030-250</t>
+        </is>
+      </c>
+      <c r="I771" s="2" t="inlineStr">
+        <is>
+          <t>http://www.hannovervinhos.com.br</t>
+        </is>
+      </c>
+      <c r="J771" s="2" t="inlineStr"/>
+      <c r="K771" s="2" t="inlineStr"/>
+      <c r="L771" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M771" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N771" s="2" t="inlineStr">
+        <is>
+          <t>hannover@hannovervinhos.com.br</t>
+        </is>
+      </c>
+      <c r="O771" s="2" t="inlineStr">
+        <is>
+          <t>+55 51 3337-3890</t>
+        </is>
+      </c>
+      <c r="P771" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q771" s="2" t="inlineStr">
+        <is>
+          <t>91636944000105</t>
+        </is>
+      </c>
+      <c r="R771" s="2" t="inlineStr"/>
+      <c r="S771" s="2" t="inlineStr"/>
+      <c r="T771" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hannovervinhos/</t>
+        </is>
+      </c>
+      <c r="U771" s="2" t="inlineStr"/>
+      <c r="V771" s="2" t="inlineStr"/>
+      <c r="W771" s="2" t="inlineStr">
+        <is>
+          <t>Sergio Fernandes</t>
+        </is>
+      </c>
+      <c r="X771" s="2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="Y771" s="2" t="inlineStr"/>
+      <c r="Z771" s="2" t="inlineStr"/>
+      <c r="AA771" s="2" t="inlineStr">
+        <is>
+          <t>https://br.linkedin.com/in/sergio-fernandes-36aa3b54/en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
